--- a/data/wwinchance.xlsx
+++ b/data/wwinchance.xlsx
@@ -11,110 +11,128 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="364">
+  <si>
+    <t>Davidson Wildcats</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Dayton Flyers</t>
+  </si>
+  <si>
+    <t>Duquesne Dukes</t>
+  </si>
+  <si>
+    <t>Fordham Rams</t>
+  </si>
+  <si>
+    <t>George Mason Patriots</t>
+  </si>
+  <si>
+    <t>George Washington Revolutionaries</t>
+  </si>
+  <si>
+    <t>La Salle Explorers</t>
+  </si>
+  <si>
+    <t>Loyola Chicago Ramblers</t>
+  </si>
+  <si>
+    <t>Rhode Island Rams</t>
+  </si>
+  <si>
+    <t>Richmond Spiders</t>
+  </si>
   <si>
     <t>Saint Louis Billikens</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>St. Bonaventure Bonnies</t>
+  </si>
+  <si>
+    <t>Saint Joseph's Hawks</t>
   </si>
   <si>
     <t>VCU Rams</t>
   </si>
   <si>
-    <t>Dayton Flyers</t>
-  </si>
-  <si>
-    <t>George Washington Revolutionaries</t>
-  </si>
-  <si>
-    <t>Saint Joseph's Hawks</t>
-  </si>
-  <si>
-    <t>George Mason Patriots</t>
-  </si>
-  <si>
-    <t>Davidson Wildcats</t>
-  </si>
-  <si>
-    <t>Duquesne Dukes</t>
-  </si>
-  <si>
-    <t>Fordham Rams</t>
-  </si>
-  <si>
-    <t>Rhode Island Rams</t>
-  </si>
-  <si>
-    <t>Richmond Spiders</t>
-  </si>
-  <si>
-    <t>St. Bonaventure Bonnies</t>
-  </si>
-  <si>
     <t>Boston College Eagles</t>
   </si>
   <si>
-    <t>La Salle Explorers</t>
-  </si>
-  <si>
-    <t>Loyola Chicago Ramblers</t>
+    <t>California Golden Bears</t>
+  </si>
+  <si>
+    <t>Clemson Tigers</t>
   </si>
   <si>
     <t>Duke Blue Devils</t>
   </si>
   <si>
+    <t>Florida State Seminoles</t>
+  </si>
+  <si>
+    <t>Georgia Tech Yellow Jackets</t>
+  </si>
+  <si>
+    <t>Louisville Cardinals</t>
+  </si>
+  <si>
+    <t>Miami Hurricanes</t>
+  </si>
+  <si>
+    <t>NC State Wolfpack</t>
+  </si>
+  <si>
+    <t>North Carolina Tar Heels</t>
+  </si>
+  <si>
+    <t>Notre Dame Fighting Irish</t>
+  </si>
+  <si>
+    <t>Pittsburgh Panthers</t>
+  </si>
+  <si>
+    <t>SMU Mustangs</t>
+  </si>
+  <si>
+    <t>Stanford Cardinal</t>
+  </si>
+  <si>
+    <t>Syracuse Orange</t>
+  </si>
+  <si>
     <t>Virginia Cavaliers</t>
   </si>
   <si>
-    <t>Miami Hurricanes</t>
-  </si>
-  <si>
-    <t>North Carolina Tar Heels</t>
-  </si>
-  <si>
-    <t>Louisville Cardinals</t>
-  </si>
-  <si>
-    <t>Clemson Tigers</t>
-  </si>
-  <si>
-    <t>SMU Mustangs</t>
-  </si>
-  <si>
-    <t>NC State Wolfpack</t>
-  </si>
-  <si>
     <t>Virginia Tech Hokies</t>
   </si>
   <si>
-    <t>Florida State Seminoles</t>
-  </si>
-  <si>
-    <t>Stanford Cardinal</t>
-  </si>
-  <si>
-    <t>California Golden Bears</t>
-  </si>
-  <si>
     <t>Wake Forest Demon Deacons</t>
   </si>
   <si>
-    <t>Syracuse Orange</t>
-  </si>
-  <si>
-    <t>Pittsburgh Panthers</t>
-  </si>
-  <si>
-    <t>Notre Dame Fighting Irish</t>
-  </si>
-  <si>
-    <t>Georgia Tech Yellow Jackets</t>
-  </si>
-  <si>
     <t>Binghamton Bearcats</t>
   </si>
   <si>
+    <t>Bryant Bulldogs</t>
+  </si>
+  <si>
+    <t>Maine Black Bears</t>
+  </si>
+  <si>
+    <t>New Hampshire Wildcats</t>
+  </si>
+  <si>
+    <t>NJIT Highlanders</t>
+  </si>
+  <si>
+    <t>UAlbany Great Danes</t>
+  </si>
+  <si>
+    <t>UMass Lowell River Hawks</t>
+  </si>
+  <si>
     <t>UMBC Retrievers</t>
   </si>
   <si>
@@ -124,154 +142,148 @@
     <t>Charlotte 49ers</t>
   </si>
   <si>
-    <t>UMass Lowell River Hawks</t>
-  </si>
-  <si>
-    <t>UAlbany Great Danes</t>
-  </si>
-  <si>
-    <t>NJIT Highlanders</t>
-  </si>
-  <si>
-    <t>Bryant Bulldogs</t>
-  </si>
-  <si>
-    <t>Maine Black Bears</t>
-  </si>
-  <si>
-    <t>New Hampshire Wildcats</t>
+    <t>East Carolina Pirates</t>
+  </si>
+  <si>
+    <t>Florida Atlantic Owls</t>
+  </si>
+  <si>
+    <t>Memphis Tigers</t>
+  </si>
+  <si>
+    <t>North Texas Mean Green</t>
+  </si>
+  <si>
+    <t>Rice Owls</t>
   </si>
   <si>
     <t>South Florida Bulls</t>
   </si>
   <si>
+    <t>Temple Owls</t>
+  </si>
+  <si>
+    <t>Tulane Green Wave</t>
+  </si>
+  <si>
     <t>Tulsa Golden Hurricane</t>
   </si>
   <si>
+    <t>UAB Blazers</t>
+  </si>
+  <si>
+    <t>UTSA Roadrunners</t>
+  </si>
+  <si>
     <t>Wichita State Shockers</t>
   </si>
   <si>
-    <t>UAB Blazers</t>
-  </si>
-  <si>
     <t>Austin Peay Governors</t>
   </si>
   <si>
-    <t>Tulane Green Wave</t>
-  </si>
-  <si>
-    <t>Florida Atlantic Owls</t>
-  </si>
-  <si>
-    <t>Memphis Tigers</t>
-  </si>
-  <si>
-    <t>North Texas Mean Green</t>
-  </si>
-  <si>
-    <t>Temple Owls</t>
-  </si>
-  <si>
-    <t>East Carolina Pirates</t>
-  </si>
-  <si>
-    <t>Rice Owls</t>
-  </si>
-  <si>
-    <t>UTSA Roadrunners</t>
+    <t>Bellarmine Knights</t>
+  </si>
+  <si>
+    <t>Central Arkansas Sugar Bears</t>
+  </si>
+  <si>
+    <t>Eastern Kentucky Colonels</t>
+  </si>
+  <si>
+    <t>Florida Gulf Coast Eagles</t>
+  </si>
+  <si>
+    <t>Jacksonville Dolphins</t>
+  </si>
+  <si>
+    <t>Lipscomb Bisons</t>
+  </si>
+  <si>
+    <t>North Alabama Lions</t>
+  </si>
+  <si>
+    <t>North Florida Ospreys</t>
+  </si>
+  <si>
+    <t>Queens University Royals</t>
+  </si>
+  <si>
+    <t>Stetson Hatters</t>
+  </si>
+  <si>
+    <t>West Georgia Wolves</t>
   </si>
   <si>
     <t>Illinois Fighting Illini</t>
   </si>
   <si>
-    <t>Central Arkansas Bears</t>
-  </si>
-  <si>
-    <t>Lipscomb Bisons</t>
-  </si>
-  <si>
-    <t>Queens University Royals</t>
-  </si>
-  <si>
-    <t>Bellarmine Knights</t>
-  </si>
-  <si>
-    <t>Florida Gulf Coast Eagles</t>
-  </si>
-  <si>
-    <t>Eastern Kentucky Colonels</t>
-  </si>
-  <si>
-    <t>Stetson Hatters</t>
-  </si>
-  <si>
-    <t>West Georgia Wolves</t>
-  </si>
-  <si>
-    <t>Jacksonville Dolphins</t>
-  </si>
-  <si>
-    <t>North Alabama Lions</t>
-  </si>
-  <si>
-    <t>North Florida Ospreys</t>
+    <t>Indiana Hoosiers</t>
+  </si>
+  <si>
+    <t>Iowa Hawkeyes</t>
+  </si>
+  <si>
+    <t>Maryland Terrapins</t>
   </si>
   <si>
     <t>Michigan Wolverines</t>
   </si>
   <si>
+    <t>Michigan State Spartans</t>
+  </si>
+  <si>
+    <t>Minnesota Golden Gophers</t>
+  </si>
+  <si>
+    <t>Nebraska Cornhuskers</t>
+  </si>
+  <si>
+    <t>Northwestern Wildcats</t>
+  </si>
+  <si>
+    <t>Ohio State Buckeyes</t>
+  </si>
+  <si>
+    <t>Oregon Ducks</t>
+  </si>
+  <si>
+    <t>Penn State Lady Lions</t>
+  </si>
+  <si>
+    <t>Purdue Boilermakers</t>
+  </si>
+  <si>
+    <t>Rutgers Scarlet Knights</t>
+  </si>
+  <si>
+    <t>UCLA Bruins</t>
+  </si>
+  <si>
+    <t>USC Trojans</t>
+  </si>
+  <si>
+    <t>Washington Huskies</t>
+  </si>
+  <si>
+    <t>Wisconsin Badgers</t>
+  </si>
+  <si>
     <t>Arizona Wildcats</t>
   </si>
   <si>
-    <t>Michigan State Spartans</t>
-  </si>
-  <si>
-    <t>Purdue Boilermakers</t>
-  </si>
-  <si>
-    <t>Nebraska Cornhuskers</t>
-  </si>
-  <si>
-    <t>Wisconsin Badgers</t>
-  </si>
-  <si>
-    <t>Ohio State Buckeyes</t>
-  </si>
-  <si>
-    <t>Iowa Hawkeyes</t>
-  </si>
-  <si>
-    <t>UCLA Bruins</t>
-  </si>
-  <si>
-    <t>Minnesota Golden Gophers</t>
-  </si>
-  <si>
-    <t>Indiana Hoosiers</t>
-  </si>
-  <si>
-    <t>Washington Huskies</t>
-  </si>
-  <si>
-    <t>USC Trojans</t>
-  </si>
-  <si>
-    <t>Northwestern Wildcats</t>
-  </si>
-  <si>
-    <t>Maryland Terrapins</t>
-  </si>
-  <si>
-    <t>Oregon Ducks</t>
-  </si>
-  <si>
-    <t>Rutgers Scarlet Knights</t>
-  </si>
-  <si>
-    <t>Penn State Nittany Lions</t>
-  </si>
-  <si>
-    <t>Texas Tech Red Raiders</t>
+    <t>Arizona State Sun Devils</t>
+  </si>
+  <si>
+    <t>Baylor Bears</t>
+  </si>
+  <si>
+    <t>BYU Cougars</t>
+  </si>
+  <si>
+    <t>Cincinnati Bearcats</t>
+  </si>
+  <si>
+    <t>Colorado Buffaloes</t>
   </si>
   <si>
     <t>Houston Cougars</t>
@@ -283,40 +295,46 @@
     <t>Kansas Jayhawks</t>
   </si>
   <si>
-    <t>Cincinnati Bearcats</t>
-  </si>
-  <si>
-    <t>BYU Cougars</t>
+    <t>Kansas State Wildcats</t>
+  </si>
+  <si>
+    <t>Oklahoma State Cowgirls</t>
+  </si>
+  <si>
+    <t>TCU Horned Frogs</t>
+  </si>
+  <si>
+    <t>Texas Tech Lady Raiders</t>
   </si>
   <si>
     <t>UCF Knights</t>
   </si>
   <si>
-    <t>TCU Horned Frogs</t>
+    <t>Utah Utes</t>
   </si>
   <si>
     <t>West Virginia Mountaineers</t>
   </si>
   <si>
-    <t>Baylor Bears</t>
-  </si>
-  <si>
-    <t>Arizona State Sun Devils</t>
-  </si>
-  <si>
-    <t>Colorado Buffaloes</t>
-  </si>
-  <si>
-    <t>Oklahoma State Cowboys</t>
-  </si>
-  <si>
     <t>Butler Bulldogs</t>
   </si>
   <si>
-    <t>Kansas State Wildcats</t>
-  </si>
-  <si>
-    <t>Utah Utes</t>
+    <t>Creighton Bluejays</t>
+  </si>
+  <si>
+    <t>DePaul Blue Demons</t>
+  </si>
+  <si>
+    <t>Georgetown Hoyas</t>
+  </si>
+  <si>
+    <t>Marquette Golden Eagles</t>
+  </si>
+  <si>
+    <t>Providence Friars</t>
+  </si>
+  <si>
+    <t>Seton Hall Pirates</t>
   </si>
   <si>
     <t>St. John's Red Storm</t>
@@ -328,28 +346,25 @@
     <t>Villanova Wildcats</t>
   </si>
   <si>
-    <t>Seton Hall Pirates</t>
-  </si>
-  <si>
-    <t>Providence Friars</t>
-  </si>
-  <si>
-    <t>DePaul Blue Demons</t>
-  </si>
-  <si>
     <t>Xavier Musketeers</t>
   </si>
   <si>
     <t>Eastern Washington Eagles</t>
   </si>
   <si>
-    <t>Creighton Bluejays</t>
-  </si>
-  <si>
-    <t>Marquette Golden Eagles</t>
-  </si>
-  <si>
-    <t>Georgetown Hoyas</t>
+    <t>Idaho Vandals</t>
+  </si>
+  <si>
+    <t>Idaho State Bengals</t>
+  </si>
+  <si>
+    <t>Montana Lady Griz</t>
+  </si>
+  <si>
+    <t>Montana State Bobcats</t>
+  </si>
+  <si>
+    <t>Northern Arizona Lumberjacks</t>
   </si>
   <si>
     <t>Northern Colorado Bears</t>
@@ -358,226 +373,235 @@
     <t>Portland State Vikings</t>
   </si>
   <si>
+    <t>Sacramento State Hornets</t>
+  </si>
+  <si>
     <t>Weber State Wildcats</t>
   </si>
   <si>
-    <t>Montana State Bobcats</t>
-  </si>
-  <si>
-    <t>Montana Grizzlies</t>
-  </si>
-  <si>
-    <t>Idaho Vandals</t>
-  </si>
-  <si>
     <t>Charleston Southern Buccaneers</t>
   </si>
   <si>
-    <t>Idaho State Bengals</t>
-  </si>
-  <si>
-    <t>Sacramento State Hornets</t>
-  </si>
-  <si>
-    <t>Northern Arizona Lumberjacks</t>
+    <t>Gardner-Webb Runnin' Bulldogs</t>
   </si>
   <si>
     <t>High Point Panthers</t>
   </si>
   <si>
+    <t>Longwood Lancers</t>
+  </si>
+  <si>
+    <t>Presbyterian Blue Hose</t>
+  </si>
+  <si>
+    <t>Radford Highlanders</t>
+  </si>
+  <si>
+    <t>South Carolina Upstate Spartans</t>
+  </si>
+  <si>
+    <t>UNC Asheville Bulldogs</t>
+  </si>
+  <si>
     <t>Winthrop Eagles</t>
   </si>
   <si>
     <t>Cal Poly Mustangs</t>
   </si>
   <si>
-    <t>Longwood Lancers</t>
-  </si>
-  <si>
-    <t>Radford Highlanders</t>
-  </si>
-  <si>
-    <t>UNC Asheville Bulldogs</t>
-  </si>
-  <si>
-    <t>Presbyterian Blue Hose</t>
-  </si>
-  <si>
-    <t>South Carolina Upstate Spartans</t>
-  </si>
-  <si>
-    <t>Gardner-Webb Runnin' Bulldogs</t>
+    <t>Cal State Bakersfield Roadrunners</t>
+  </si>
+  <si>
+    <t>Cal State Fullerton Titans</t>
+  </si>
+  <si>
+    <t>Cal State Northridge Matadors</t>
+  </si>
+  <si>
+    <t>Hawai'i Rainbow Wahine</t>
+  </si>
+  <si>
+    <t>Long Beach State Beach</t>
+  </si>
+  <si>
+    <t>UC Davis Aggies</t>
   </si>
   <si>
     <t>UC Irvine Anteaters</t>
   </si>
   <si>
+    <t>UC Riverside Highlanders</t>
+  </si>
+  <si>
     <t>UC San Diego Tritons</t>
   </si>
   <si>
-    <t>Hawai'i Rainbow Warriors</t>
-  </si>
-  <si>
-    <t>Cal State Northridge Matadors</t>
-  </si>
-  <si>
     <t>UC Santa Barbara Gauchos</t>
   </si>
   <si>
-    <t>UC Davis Aggies</t>
-  </si>
-  <si>
-    <t>Cal State Fullerton Titans</t>
-  </si>
-  <si>
     <t>Campbell Fighting Camels</t>
   </si>
   <si>
-    <t>UC Riverside Highlanders</t>
-  </si>
-  <si>
-    <t>Long Beach State Beach</t>
-  </si>
-  <si>
-    <t>Cal State Bakersfield Roadrunners</t>
+    <t>Charleston Cougars</t>
+  </si>
+  <si>
+    <t>Drexel Dragons</t>
+  </si>
+  <si>
+    <t>Elon Phoenix</t>
+  </si>
+  <si>
+    <t>Hampton Lady Pirates</t>
+  </si>
+  <si>
+    <t>Hofstra Pride</t>
+  </si>
+  <si>
+    <t>Monmouth Hawks</t>
+  </si>
+  <si>
+    <t>North Carolina A&amp;T Aggies</t>
+  </si>
+  <si>
+    <t>Northeastern Huskies</t>
+  </si>
+  <si>
+    <t>Stony Brook Seawolves</t>
+  </si>
+  <si>
+    <t>Towson Tigers</t>
   </si>
   <si>
     <t>UNC Wilmington Seahawks</t>
   </si>
   <si>
-    <t>Hofstra Pride</t>
-  </si>
-  <si>
-    <t>Charleston Cougars</t>
-  </si>
-  <si>
     <t>William &amp; Mary Tribe</t>
   </si>
   <si>
-    <t>Monmouth Hawks</t>
-  </si>
-  <si>
-    <t>Towson Tigers</t>
-  </si>
-  <si>
-    <t>Drexel Dragons</t>
-  </si>
-  <si>
-    <t>Stony Brook Seawolves</t>
+    <t>Delaware Blue Hens</t>
   </si>
   <si>
     <t>Florida International Panthers</t>
   </si>
   <si>
-    <t>Hampton Pirates</t>
-  </si>
-  <si>
-    <t>North Carolina A&amp;T Aggies</t>
-  </si>
-  <si>
-    <t>Elon Phoenix</t>
-  </si>
-  <si>
-    <t>Delaware Blue Hens</t>
-  </si>
-  <si>
-    <t>Northeastern Huskies</t>
+    <t>Jacksonville State Gamecocks</t>
+  </si>
+  <si>
+    <t>Kennesaw State Owls</t>
   </si>
   <si>
     <t>Liberty Flames</t>
   </si>
   <si>
+    <t>Louisiana Tech Lady Techsters</t>
+  </si>
+  <si>
+    <t>Missouri State Bears</t>
+  </si>
+  <si>
+    <t>Middle Tennessee Blue Raiders</t>
+  </si>
+  <si>
+    <t>New Mexico State Aggies</t>
+  </si>
+  <si>
     <t>Sam Houston Bearkats</t>
   </si>
   <si>
-    <t>Western Kentucky Hilltoppers</t>
-  </si>
-  <si>
-    <t>Kennesaw State Owls</t>
-  </si>
-  <si>
-    <t>New Mexico State Aggies</t>
-  </si>
-  <si>
-    <t>Middle Tennessee Blue Raiders</t>
-  </si>
-  <si>
-    <t>Jacksonville State Gamecocks</t>
-  </si>
-  <si>
-    <t>Louisiana Tech Bulldogs</t>
-  </si>
-  <si>
-    <t>Missouri State Bears</t>
-  </si>
-  <si>
     <t>UTEP Miners</t>
   </si>
   <si>
+    <t>Western Kentucky Lady Toppers</t>
+  </si>
+  <si>
+    <t>Cleveland State Vikings</t>
+  </si>
+  <si>
+    <t>Detroit Mercy Titans</t>
+  </si>
+  <si>
+    <t>Green Bay Phoenix</t>
+  </si>
+  <si>
+    <t>IU Indianapolis Jaguars</t>
+  </si>
+  <si>
+    <t>Milwaukee Panthers</t>
+  </si>
+  <si>
+    <t>Northern Kentucky Norse</t>
+  </si>
+  <si>
+    <t>Oakland Golden Grizzlies</t>
+  </si>
+  <si>
+    <t>Purdue Fort Wayne Mastodons</t>
+  </si>
+  <si>
     <t>Robert Morris Colonials</t>
   </si>
   <si>
     <t>Wright State Raiders</t>
   </si>
   <si>
-    <t>Detroit Mercy Titans</t>
-  </si>
-  <si>
-    <t>Green Bay Phoenix</t>
-  </si>
-  <si>
     <t>Youngstown State Penguins</t>
   </si>
   <si>
-    <t>Northern Kentucky Norse</t>
-  </si>
-  <si>
-    <t>Oakland Golden Grizzlies</t>
-  </si>
-  <si>
-    <t>Purdue Fort Wayne Mastodons</t>
-  </si>
-  <si>
-    <t>Milwaukee Panthers</t>
-  </si>
-  <si>
-    <t>Cleveland State Vikings</t>
-  </si>
-  <si>
-    <t>IU Indianapolis Jaguars</t>
+    <t>Brown Bears</t>
+  </si>
+  <si>
+    <t>Columbia Lions</t>
+  </si>
+  <si>
+    <t>Cornell Big Red</t>
+  </si>
+  <si>
+    <t>Dartmouth Big Green</t>
+  </si>
+  <si>
+    <t>Harvard Crimson</t>
+  </si>
+  <si>
+    <t>Pennsylvania Quakers</t>
+  </si>
+  <si>
+    <t>Princeton Tigers</t>
   </si>
   <si>
     <t>Yale Bulldogs</t>
   </si>
   <si>
-    <t>Harvard Crimson</t>
-  </si>
-  <si>
-    <t>Pennsylvania Quakers</t>
-  </si>
-  <si>
-    <t>Cornell Big Red</t>
-  </si>
-  <si>
-    <t>Columbia Lions</t>
-  </si>
-  <si>
-    <t>Princeton Tigers</t>
-  </si>
-  <si>
-    <t>Brown Bears</t>
-  </si>
-  <si>
-    <t>Dartmouth Big Green</t>
+    <t>Canisius Golden Griffins</t>
+  </si>
+  <si>
+    <t>Fairfield Stags</t>
+  </si>
+  <si>
+    <t>Iona Gaels</t>
+  </si>
+  <si>
+    <t>Manhattan Jaspers</t>
+  </si>
+  <si>
+    <t>Marist Red Foxes</t>
   </si>
   <si>
     <t>Merrimack Warriors</t>
   </si>
   <si>
-    <t>Fairfield Stags</t>
-  </si>
-  <si>
-    <t>Marist Red Foxes</t>
+    <t>Mount St. Mary's Mountaineers</t>
+  </si>
+  <si>
+    <t>Niagara Purple Eagles</t>
+  </si>
+  <si>
+    <t>Quinnipiac Bobcats</t>
+  </si>
+  <si>
+    <t>Rider Broncs</t>
+  </si>
+  <si>
+    <t>Sacred Heart Pioneers</t>
   </si>
   <si>
     <t>Siena Saints</t>
@@ -586,88 +610,85 @@
     <t>Saint Peter's Peacocks</t>
   </si>
   <si>
-    <t>Quinnipiac Bobcats</t>
-  </si>
-  <si>
-    <t>Iona Gaels</t>
-  </si>
-  <si>
-    <t>Mount St. Mary's Mountaineers</t>
-  </si>
-  <si>
-    <t>Sacred Heart Pioneers</t>
-  </si>
-  <si>
-    <t>Manhattan Jaspers</t>
-  </si>
-  <si>
-    <t>Niagara Purple Eagles</t>
-  </si>
-  <si>
-    <t>Canisius Golden Griffins</t>
-  </si>
-  <si>
-    <t>Rider Broncs</t>
+    <t>Akron Zips</t>
+  </si>
+  <si>
+    <t>Ball State Cardinals</t>
+  </si>
+  <si>
+    <t>Bowling Green Falcons</t>
+  </si>
+  <si>
+    <t>Buffalo Bulls</t>
+  </si>
+  <si>
+    <t>Central Michigan Chippewas</t>
+  </si>
+  <si>
+    <t>Eastern Michigan Eagles</t>
+  </si>
+  <si>
+    <t>Kent State Golden Flashes</t>
   </si>
   <si>
     <t>Miami (OH) RedHawks</t>
   </si>
   <si>
-    <t>Akron Zips</t>
-  </si>
-  <si>
-    <t>Kent State Golden Flashes</t>
+    <t>Northern Illinois Huskies</t>
+  </si>
+  <si>
+    <t>Ohio Bobcats</t>
   </si>
   <si>
     <t>Toledo Rockets</t>
   </si>
   <si>
-    <t>Bowling Green Falcons</t>
-  </si>
-  <si>
-    <t>Ohio Bobcats</t>
-  </si>
-  <si>
-    <t>Buffalo Bulls</t>
-  </si>
-  <si>
-    <t>Massachusetts Minutemen</t>
-  </si>
-  <si>
-    <t>Central Michigan Chippewas</t>
-  </si>
-  <si>
-    <t>Eastern Michigan Eagles</t>
-  </si>
-  <si>
-    <t>Ball State Cardinals</t>
-  </si>
-  <si>
-    <t>Northern Illinois Huskies</t>
+    <t>Massachusetts Minutewomen</t>
+  </si>
+  <si>
+    <t>Western Michigan Broncos</t>
+  </si>
+  <si>
+    <t>Coppin State Eagles</t>
+  </si>
+  <si>
+    <t>Delaware State Hornets</t>
   </si>
   <si>
     <t>Howard Bison</t>
   </si>
   <si>
+    <t>Maryland Eastern Shore Hawks</t>
+  </si>
+  <si>
+    <t>Morgan State Lady Bears</t>
+  </si>
+  <si>
+    <t>North Carolina Central Eagles</t>
+  </si>
+  <si>
     <t>Norfolk State Spartans</t>
   </si>
   <si>
-    <t>Western Michigan Broncos</t>
-  </si>
-  <si>
-    <t>Morgan State Bears</t>
-  </si>
-  <si>
-    <t>North Carolina Central Eagles</t>
-  </si>
-  <si>
-    <t>Maryland Eastern Shore Hawks</t>
-  </si>
-  <si>
-    <t>Coppin State Eagles</t>
-  </si>
-  <si>
-    <t>Delaware State Hornets</t>
+    <t>South Carolina State Lady Bulldogs</t>
+  </si>
+  <si>
+    <t>Air Force Falcons</t>
+  </si>
+  <si>
+    <t>Boise State Broncos</t>
+  </si>
+  <si>
+    <t>Colorado State Rams</t>
+  </si>
+  <si>
+    <t>Fresno State Bulldogs</t>
+  </si>
+  <si>
+    <t>Grand Canyon Lopes</t>
+  </si>
+  <si>
+    <t>Nevada Wolf Pack</t>
   </si>
   <si>
     <t>New Mexico Lobos</t>
@@ -676,298 +697,274 @@
     <t>San Diego State Aztecs</t>
   </si>
   <si>
-    <t>Grand Canyon Lopes</t>
-  </si>
-  <si>
-    <t>Boise State Broncos</t>
-  </si>
-  <si>
-    <t>Nevada Wolf Pack</t>
-  </si>
-  <si>
-    <t>Colorado State Rams</t>
-  </si>
-  <si>
-    <t>UNLV Rebels</t>
-  </si>
-  <si>
-    <t>Fresno State Bulldogs</t>
-  </si>
-  <si>
     <t>San Jose State Spartans</t>
   </si>
   <si>
-    <t>South Carolina State Bulldogs</t>
-  </si>
-  <si>
-    <t>Air Force Falcons</t>
+    <t>UNLV Lady Rebels</t>
   </si>
   <si>
     <t>Utah State Aggies</t>
   </si>
   <si>
+    <t>Wyoming Cowgirls</t>
+  </si>
+  <si>
     <t>Belmont Bruins</t>
   </si>
   <si>
+    <t>Bradley Braves</t>
+  </si>
+  <si>
+    <t>Drake Bulldogs</t>
+  </si>
+  <si>
+    <t>Evansville Purple Aces</t>
+  </si>
+  <si>
+    <t>Illinois State Redbirds</t>
+  </si>
+  <si>
+    <t>Indiana State Sycamores</t>
+  </si>
+  <si>
+    <t>Murray State Racers</t>
+  </si>
+  <si>
+    <t>Northern Iowa Panthers</t>
+  </si>
+  <si>
+    <t>Southern Illinois Salukis</t>
+  </si>
+  <si>
     <t>UIC Flames</t>
   </si>
   <si>
-    <t>Bradley Braves</t>
-  </si>
-  <si>
-    <t>Northern Iowa Panthers</t>
-  </si>
-  <si>
-    <t>Illinois State Redbirds</t>
-  </si>
-  <si>
-    <t>Southern Illinois Salukis</t>
-  </si>
-  <si>
-    <t>Wyoming Cowboys</t>
-  </si>
-  <si>
-    <t>Murray State Racers</t>
-  </si>
-  <si>
-    <t>Drake Bulldogs</t>
-  </si>
-  <si>
-    <t>Indiana State Sycamores</t>
-  </si>
-  <si>
-    <t>Evansville Purple Aces</t>
-  </si>
-  <si>
     <t>Valparaiso Beacons</t>
   </si>
   <si>
+    <t>Central Connecticut Blue Devils</t>
+  </si>
+  <si>
+    <t>Chicago State Cougars</t>
+  </si>
+  <si>
+    <t>Fairleigh Dickinson Knights</t>
+  </si>
+  <si>
+    <t>Le Moyne Dolphins</t>
+  </si>
+  <si>
     <t>Long Island University Sharks</t>
   </si>
   <si>
     <t>Mercyhurst Lakers</t>
   </si>
   <si>
-    <t>Central Connecticut Blue Devils</t>
-  </si>
-  <si>
     <t>New Haven Chargers</t>
   </si>
   <si>
-    <t>Le Moyne Dolphins</t>
-  </si>
-  <si>
-    <t>Fairleigh Dickinson Knights</t>
-  </si>
-  <si>
-    <t>Chicago State Cougars</t>
-  </si>
-  <si>
     <t>Saint Francis Red Flash</t>
   </si>
   <si>
+    <t>Stonehill Skyhawks</t>
+  </si>
+  <si>
+    <t>Wagner Seahawks</t>
+  </si>
+  <si>
+    <t>Eastern Illinois Panthers</t>
+  </si>
+  <si>
+    <t>Lindenwood Lions</t>
+  </si>
+  <si>
+    <t>Little Rock Trojans</t>
+  </si>
+  <si>
+    <t>Morehead State Eagles</t>
+  </si>
+  <si>
     <t>Southeast Missouri State Redhawks</t>
   </si>
   <si>
-    <t>Tennessee State Tigers</t>
-  </si>
-  <si>
-    <t>Morehead State Eagles</t>
-  </si>
-  <si>
     <t>SIU Edwardsville Cougars</t>
   </si>
   <si>
-    <t>Lindenwood Lions</t>
+    <t>Southern Indiana Screaming Eagles</t>
+  </si>
+  <si>
+    <t>Tennessee State Lady Tigers</t>
   </si>
   <si>
     <t>Tennessee Tech Golden Eagles</t>
   </si>
   <si>
-    <t>Little Rock Trojans</t>
-  </si>
-  <si>
-    <t>Wagner Seahawks</t>
-  </si>
-  <si>
-    <t>Eastern Illinois Panthers</t>
-  </si>
-  <si>
-    <t>Stonehill Skyhawks</t>
-  </si>
-  <si>
-    <t>Southern Indiana Screaming Eagles</t>
-  </si>
-  <si>
     <t>UT Martin Skyhawks</t>
   </si>
   <si>
+    <t>Western Illinois Leathernecks</t>
+  </si>
+  <si>
+    <t>American University Eagles</t>
+  </si>
+  <si>
+    <t>Army Black Knights</t>
+  </si>
+  <si>
     <t>Boston University Terriers</t>
   </si>
   <si>
+    <t>Bucknell Bison</t>
+  </si>
+  <si>
     <t>Colgate Raiders</t>
   </si>
   <si>
-    <t>American University Eagles</t>
+    <t>Holy Cross Crusaders</t>
+  </si>
+  <si>
+    <t>Lafayette Leopards</t>
   </si>
   <si>
     <t>Lehigh Mountain Hawks</t>
   </si>
   <si>
-    <t>Lafayette Leopards</t>
-  </si>
-  <si>
-    <t>Holy Cross Crusaders</t>
-  </si>
-  <si>
-    <t>Army Black Knights</t>
-  </si>
-  <si>
-    <t>Bucknell Bison</t>
-  </si>
-  <si>
-    <t>Western Illinois Leathernecks</t>
+    <t>Loyola Maryland Greyhounds</t>
+  </si>
+  <si>
+    <t>Navy Midshipmen</t>
+  </si>
+  <si>
+    <t>Alabama Crimson Tide</t>
+  </si>
+  <si>
+    <t>Arkansas Razorbacks</t>
+  </si>
+  <si>
+    <t>Auburn Tigers</t>
   </si>
   <si>
     <t>Florida Gators</t>
   </si>
   <si>
-    <t>Alabama Crimson Tide</t>
-  </si>
-  <si>
-    <t>Tennessee Volunteers</t>
+    <t>Georgia Lady Bulldogs</t>
   </si>
   <si>
     <t>Kentucky Wildcats</t>
   </si>
   <si>
-    <t>Arkansas Razorbacks</t>
+    <t>LSU Tigers</t>
+  </si>
+  <si>
+    <t>Mississippi State Bulldogs</t>
+  </si>
+  <si>
+    <t>Missouri Tigers</t>
+  </si>
+  <si>
+    <t>Oklahoma Sooners</t>
+  </si>
+  <si>
+    <t>Ole Miss Rebels</t>
+  </si>
+  <si>
+    <t>South Carolina Gamecocks</t>
+  </si>
+  <si>
+    <t>Tennessee Lady Volunteers</t>
   </si>
   <si>
     <t>Texas Longhorns</t>
   </si>
   <si>
-    <t>Georgia Bulldogs</t>
-  </si>
-  <si>
-    <t>Navy Midshipmen</t>
-  </si>
-  <si>
-    <t>Missouri Tigers</t>
-  </si>
-  <si>
-    <t>Oklahoma Sooners</t>
-  </si>
-  <si>
-    <t>Auburn Tigers</t>
-  </si>
-  <si>
-    <t>Mississippi State Bulldogs</t>
-  </si>
-  <si>
-    <t>LSU Tigers</t>
-  </si>
-  <si>
-    <t>Ole Miss Rebels</t>
-  </si>
-  <si>
-    <t>South Carolina Gamecocks</t>
-  </si>
-  <si>
-    <t>Loyola Maryland Greyhounds</t>
+    <t>Texas A&amp;M Aggies</t>
   </si>
   <si>
     <t>Vanderbilt Commodores</t>
   </si>
   <si>
-    <t>Texas A&amp;M Aggies</t>
-  </si>
-  <si>
-    <t>East Tennessee State Buccaneers</t>
+    <t>Chattanooga Mocs</t>
+  </si>
+  <si>
+    <t>East Tennessee State Bucs</t>
+  </si>
+  <si>
+    <t>Furman Paladins</t>
+  </si>
+  <si>
+    <t>Mercer Bears</t>
   </si>
   <si>
     <t>Samford Bulldogs</t>
   </si>
   <si>
-    <t>Mercer Bears</t>
-  </si>
-  <si>
-    <t>Furman Paladins</t>
-  </si>
-  <si>
-    <t>Chattanooga Mocs</t>
-  </si>
-  <si>
     <t>UNC Greensboro Spartans</t>
   </si>
   <si>
-    <t>The Citadel Bulldogs</t>
-  </si>
-  <si>
-    <t>VMI Keydets</t>
-  </si>
-  <si>
-    <t>McNeese Cowboys</t>
-  </si>
-  <si>
-    <t>Stephen F. Austin Lumberjacks</t>
+    <t>Western Carolina Catamounts</t>
+  </si>
+  <si>
+    <t>Wofford Terriers</t>
+  </si>
+  <si>
+    <t>East Texas A&amp;M Lions</t>
+  </si>
+  <si>
+    <t>Houston Christian Huskies</t>
+  </si>
+  <si>
+    <t>Incarnate Word Cardinals</t>
+  </si>
+  <si>
+    <t>Lamar Cardinals</t>
+  </si>
+  <si>
+    <t>McNeese Cowgirls</t>
   </si>
   <si>
     <t>New Orleans Privateers</t>
   </si>
   <si>
-    <t>Western Carolina Catamounts</t>
-  </si>
-  <si>
-    <t>Wofford Terriers</t>
-  </si>
-  <si>
     <t>Nicholls Colonels</t>
   </si>
   <si>
-    <t>Northwestern State Demons</t>
-  </si>
-  <si>
-    <t>Lamar Cardinals</t>
-  </si>
-  <si>
-    <t>Incarnate Word Cardinals</t>
-  </si>
-  <si>
-    <t>Houston Christian Huskies</t>
-  </si>
-  <si>
-    <t>East Texas A&amp;M Lions</t>
-  </si>
-  <si>
-    <t>SE Louisiana Lions</t>
+    <t>Northwestern State Lady Demons</t>
+  </si>
+  <si>
+    <t>SE Louisiana Lady Lions</t>
+  </si>
+  <si>
+    <t>Stephen F. Austin Ladyjacks</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M-Corpus Christi Islanders</t>
+  </si>
+  <si>
+    <t>UT Rio Grande Valley Vaqueros</t>
+  </si>
+  <si>
+    <t>Denver Pioneers</t>
+  </si>
+  <si>
+    <t>Kansas City Roos</t>
+  </si>
+  <si>
+    <t>North Dakota Fighting Hawks</t>
   </si>
   <si>
     <t>North Dakota State Bison</t>
   </si>
   <si>
-    <t>UT Rio Grande Valley Vaqueros</t>
-  </si>
-  <si>
     <t>Omaha Mavericks</t>
   </si>
   <si>
-    <t>Texas A&amp;M-Corpus Christi Islanders</t>
-  </si>
-  <si>
-    <t>Denver Pioneers</t>
-  </si>
-  <si>
-    <t>North Dakota Fighting Hawks</t>
+    <t>Oral Roberts Golden Eagles</t>
   </si>
   <si>
     <t>South Dakota Coyotes</t>
   </si>
   <si>
-    <t>Oral Roberts Golden Eagles</t>
-  </si>
-  <si>
-    <t>Kansas City Roos</t>
+    <t>South Dakota State Jackrabbits</t>
   </si>
   <si>
     <t>St. Thomas-Minnesota Tommies</t>
@@ -1003,7 +1000,7 @@
     <t>South Alabama Jaguars</t>
   </si>
   <si>
-    <t>Southern Miss Golden Eagles</t>
+    <t>Southern Miss Lady Eagles</t>
   </si>
   <si>
     <t>Texas State Bobcats</t>
@@ -1015,97 +1012,97 @@
     <t>UL Monroe Warhawks</t>
   </si>
   <si>
+    <t>Alabama A&amp;M Bulldogs</t>
+  </si>
+  <si>
+    <t>Alabama State Lady Hornets</t>
+  </si>
+  <si>
+    <t>Alcorn State Lady Braves</t>
+  </si>
+  <si>
+    <t>Arkansas-Pine Bluff Golden Lions</t>
+  </si>
+  <si>
     <t>Bethune-Cookman Wildcats</t>
   </si>
   <si>
-    <t>Alabama A&amp;M Bulldogs</t>
-  </si>
-  <si>
     <t>Florida A&amp;M Rattlers</t>
   </si>
   <si>
-    <t>Prairie View A&amp;M Panthers</t>
-  </si>
-  <si>
-    <t>Alabama State Hornets</t>
-  </si>
-  <si>
-    <t>Grambling Tigers</t>
-  </si>
-  <si>
-    <t>Arkansas-Pine Bluff Golden Lions</t>
-  </si>
-  <si>
-    <t>Jackson State Tigers</t>
-  </si>
-  <si>
-    <t>Alcorn State Braves</t>
-  </si>
-  <si>
-    <t>Mississippi Valley State Delta Devils</t>
+    <t>Grambling Lady Tigers</t>
+  </si>
+  <si>
+    <t>Jackson State Lady Tigers</t>
+  </si>
+  <si>
+    <t>Mississippi Valley State Devilettes</t>
+  </si>
+  <si>
+    <t>Prairie View A&amp;M Lady Panthers</t>
+  </si>
+  <si>
+    <t>Southern Jaguars</t>
+  </si>
+  <si>
+    <t>Texas Southern Tigers</t>
+  </si>
+  <si>
+    <t>Abilene Christian Wildcats</t>
+  </si>
+  <si>
+    <t>California Baptist Lancers</t>
+  </si>
+  <si>
+    <t>Southern Utah Thunderbirds</t>
+  </si>
+  <si>
+    <t>Tarleton State Texans</t>
+  </si>
+  <si>
+    <t>UT Arlington Mavericks</t>
+  </si>
+  <si>
+    <t>Utah Tech Trailblazers</t>
   </si>
   <si>
     <t>Utah Valley Wolverines</t>
   </si>
   <si>
-    <t>California Baptist Lancers</t>
-  </si>
-  <si>
-    <t>Utah Tech Trailblazers</t>
-  </si>
-  <si>
-    <t>UT Arlington Mavericks</t>
-  </si>
-  <si>
-    <t>Abilene Christian Wildcats</t>
-  </si>
-  <si>
-    <t>Southern Utah Thunderbirds</t>
-  </si>
-  <si>
-    <t>Tarleton State Texans</t>
-  </si>
-  <si>
-    <t>Texas Southern Tigers</t>
-  </si>
-  <si>
-    <t>Southern Jaguars</t>
+    <t>Gonzaga Bulldogs</t>
+  </si>
+  <si>
+    <t>Loyola Marymount Lions</t>
+  </si>
+  <si>
+    <t>Oregon State Beavers</t>
+  </si>
+  <si>
+    <t>Pacific Tigers</t>
+  </si>
+  <si>
+    <t>Pepperdine Waves</t>
+  </si>
+  <si>
+    <t>Portland Pilots</t>
+  </si>
+  <si>
+    <t>San Diego Toreros</t>
+  </si>
+  <si>
+    <t>San Francisco Dons</t>
+  </si>
+  <si>
+    <t>Santa Clara Broncos</t>
+  </si>
+  <si>
+    <t>Seattle U Redhawks</t>
   </si>
   <si>
     <t>Saint Mary's Gaels</t>
   </si>
   <si>
-    <t>Gonzaga Bulldogs</t>
-  </si>
-  <si>
-    <t>Santa Clara Broncos</t>
-  </si>
-  <si>
-    <t>Seattle U Redhawks</t>
-  </si>
-  <si>
-    <t>San Francisco Dons</t>
-  </si>
-  <si>
-    <t>Oregon State Beavers</t>
-  </si>
-  <si>
-    <t>Pacific Tigers</t>
-  </si>
-  <si>
     <t>Washington State Cougars</t>
-  </si>
-  <si>
-    <t>Loyola Marymount Lions</t>
-  </si>
-  <si>
-    <t>Portland Pilots</t>
-  </si>
-  <si>
-    <t>San Diego Toreros</t>
-  </si>
-  <si>
-    <t>Pepperdine Waves</t>
   </si>
 </sst>
 </file>
@@ -1367,6 +1364,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="27.75"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -4106,7 +4106,7 @@
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>1</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>1</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>1</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>1</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>1</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>1</v>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>1</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>1</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>1</v>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1</v>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1</v>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1</v>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1</v>

--- a/data/wwinchance.xlsx
+++ b/data/wwinchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="364">
   <si>
     <t>Davidson Wildcats</t>
   </si>
@@ -514,37 +514,37 @@
     <t>Western Kentucky Lady Toppers</t>
   </si>
   <si>
+    <t>Green Bay Phoenix</t>
+  </si>
+  <si>
+    <t>Youngstown State Penguins</t>
+  </si>
+  <si>
     <t>Cleveland State Vikings</t>
   </si>
   <si>
+    <t>Northern Kentucky Norse</t>
+  </si>
+  <si>
+    <t>Purdue Fort Wayne Mastodons</t>
+  </si>
+  <si>
+    <t>Robert Morris Colonials</t>
+  </si>
+  <si>
+    <t>IU Indianapolis Jaguars</t>
+  </si>
+  <si>
+    <t>Oakland Golden Grizzlies</t>
+  </si>
+  <si>
+    <t>Wright State Raiders</t>
+  </si>
+  <si>
+    <t>Milwaukee Panthers</t>
+  </si>
+  <si>
     <t>Detroit Mercy Titans</t>
-  </si>
-  <si>
-    <t>Green Bay Phoenix</t>
-  </si>
-  <si>
-    <t>IU Indianapolis Jaguars</t>
-  </si>
-  <si>
-    <t>Milwaukee Panthers</t>
-  </si>
-  <si>
-    <t>Northern Kentucky Norse</t>
-  </si>
-  <si>
-    <t>Oakland Golden Grizzlies</t>
-  </si>
-  <si>
-    <t>Purdue Fort Wayne Mastodons</t>
-  </si>
-  <si>
-    <t>Robert Morris Colonials</t>
-  </si>
-  <si>
-    <t>Wright State Raiders</t>
-  </si>
-  <si>
-    <t>Youngstown State Penguins</t>
   </si>
   <si>
     <t>Brown Bears</t>
@@ -1138,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1147,6 +1147,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2700,88 +2703,88 @@
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>1</v>
+      <c r="B167" s="3">
+        <v>33.48488597</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>1</v>
+      <c r="B168" s="3">
+        <v>25.38271914</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>1</v>
+      <c r="B169" s="3">
+        <v>22.92767103</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>1</v>
+      <c r="B170" s="3">
+        <v>6.635264745</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>1</v>
+      <c r="B171" s="3">
+        <v>5.56454716</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>1</v>
+      <c r="B172" s="3">
+        <v>3.376543095</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>1</v>
+      <c r="B173" s="3">
+        <v>1.578010014</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>1</v>
+      <c r="B174" s="3">
+        <v>0.5758562575</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>1</v>
+      <c r="B175" s="3">
+        <v>0.3921245042</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>1</v>
+      <c r="B176" s="3">
+        <v>0.04135951171</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>1</v>
+      <c r="B177" s="3">
+        <v>0.04101857436</v>
       </c>
     </row>
     <row r="178">

--- a/data/wwinchance.xlsx
+++ b/data/wwinchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="364">
   <si>
     <t>Davidson Wildcats</t>
   </si>
@@ -178,42 +178,42 @@
     <t>Wichita State Shockers</t>
   </si>
   <si>
+    <t>Eastern Kentucky Colonels</t>
+  </si>
+  <si>
+    <t>Central Arkansas Sugar Bears</t>
+  </si>
+  <si>
+    <t>Jacksonville Dolphins</t>
+  </si>
+  <si>
+    <t>Stetson Hatters</t>
+  </si>
+  <si>
+    <t>Florida Gulf Coast Eagles</t>
+  </si>
+  <si>
+    <t>North Alabama Lions</t>
+  </si>
+  <si>
     <t>Austin Peay Governors</t>
   </si>
   <si>
+    <t>West Georgia Wolves</t>
+  </si>
+  <si>
+    <t>Lipscomb Bisons</t>
+  </si>
+  <si>
+    <t>North Florida Ospreys</t>
+  </si>
+  <si>
+    <t>Queens University Royals</t>
+  </si>
+  <si>
     <t>Bellarmine Knights</t>
   </si>
   <si>
-    <t>Central Arkansas Sugar Bears</t>
-  </si>
-  <si>
-    <t>Eastern Kentucky Colonels</t>
-  </si>
-  <si>
-    <t>Florida Gulf Coast Eagles</t>
-  </si>
-  <si>
-    <t>Jacksonville Dolphins</t>
-  </si>
-  <si>
-    <t>Lipscomb Bisons</t>
-  </si>
-  <si>
-    <t>North Alabama Lions</t>
-  </si>
-  <si>
-    <t>North Florida Ospreys</t>
-  </si>
-  <si>
-    <t>Queens University Royals</t>
-  </si>
-  <si>
-    <t>Stetson Hatters</t>
-  </si>
-  <si>
-    <t>West Georgia Wolves</t>
-  </si>
-  <si>
     <t>Illinois Fighting Illini</t>
   </si>
   <si>
@@ -970,46 +970,46 @@
     <t>St. Thomas-Minnesota Tommies</t>
   </si>
   <si>
+    <t>James Madison Dukes</t>
+  </si>
+  <si>
+    <t>Georgia Southern Eagles</t>
+  </si>
+  <si>
+    <t>Troy Trojans</t>
+  </si>
+  <si>
+    <t>Arkansas State Red Wolves</t>
+  </si>
+  <si>
+    <t>Marshall Thundering Herd</t>
+  </si>
+  <si>
+    <t>Old Dominion Monarchs</t>
+  </si>
+  <si>
+    <t>UL Monroe Warhawks</t>
+  </si>
+  <si>
+    <t>Coastal Carolina Chanticleers</t>
+  </si>
+  <si>
+    <t>Southern Miss Lady Eagles</t>
+  </si>
+  <si>
+    <t>South Alabama Jaguars</t>
+  </si>
+  <si>
     <t>App State Mountaineers</t>
   </si>
   <si>
-    <t>Arkansas State Red Wolves</t>
-  </si>
-  <si>
-    <t>Coastal Carolina Chanticleers</t>
-  </si>
-  <si>
-    <t>Georgia Southern Eagles</t>
+    <t>Texas State Bobcats</t>
   </si>
   <si>
     <t>Georgia State Panthers</t>
   </si>
   <si>
-    <t>James Madison Dukes</t>
-  </si>
-  <si>
     <t>Louisiana Ragin' Cajuns</t>
-  </si>
-  <si>
-    <t>Marshall Thundering Herd</t>
-  </si>
-  <si>
-    <t>Old Dominion Monarchs</t>
-  </si>
-  <si>
-    <t>South Alabama Jaguars</t>
-  </si>
-  <si>
-    <t>Southern Miss Lady Eagles</t>
-  </si>
-  <si>
-    <t>Texas State Bobcats</t>
-  </si>
-  <si>
-    <t>Troy Trojans</t>
-  </si>
-  <si>
-    <t>UL Monroe Warhawks</t>
   </si>
   <si>
     <t>Alabama A&amp;M Bulldogs</t>
@@ -1138,7 +1138,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1147,6 +1147,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -1807,96 +1810,96 @@
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>1</v>
+      <c r="B55" s="3">
+        <v>25.64638029</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>1</v>
+      <c r="B56" s="3">
+        <v>21.91696225</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>1</v>
+      <c r="B57" s="3">
+        <v>20.40964788</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>1</v>
+      <c r="B58" s="3">
+        <v>12.34721876</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>1</v>
+      <c r="B59" s="3">
+        <v>8.286078591</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1</v>
+      <c r="B60" s="3">
+        <v>4.11929145</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1</v>
+      <c r="B61" s="3">
+        <v>3.40906012</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>1</v>
+      <c r="B62" s="3">
+        <v>2.320461354</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>1</v>
+      <c r="B63" s="3">
+        <v>0.9693627795</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>1</v>
+      <c r="B64" s="3">
+        <v>0.3883976495</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>1</v>
+      <c r="B65" s="3">
+        <v>0.1865564575</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>1</v>
+      <c r="B66" s="3">
+        <v>5.82418543E-4</v>
       </c>
     </row>
     <row r="67">
@@ -2703,88 +2706,88 @@
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="3">
-        <v>33.48488597</v>
+      <c r="B167" s="4">
+        <v>33.30592402</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="3">
-        <v>25.38271914</v>
+      <c r="B168" s="4">
+        <v>25.44474679</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="3">
-        <v>22.92767103</v>
+      <c r="B169" s="4">
+        <v>22.98369929</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="3">
-        <v>6.635264745</v>
+      <c r="B170" s="4">
+        <v>6.651479315</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="3">
-        <v>5.56454716</v>
+      <c r="B171" s="4">
+        <v>5.578145222</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="3">
-        <v>3.376543095</v>
+      <c r="B172" s="4">
+        <v>3.38479434</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="3">
-        <v>1.578010014</v>
+      <c r="B173" s="4">
+        <v>1.581866191</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="3">
-        <v>0.5758562575</v>
+      <c r="B174" s="4">
+        <v>0.5772634753</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="3">
-        <v>0.3921245042</v>
+      <c r="B175" s="4">
+        <v>0.3930827373</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="3">
-        <v>0.04135951171</v>
+      <c r="B176" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="3">
-        <v>0.04101857436</v>
+      <c r="B177" s="4">
+        <v>0.09899861912</v>
       </c>
     </row>
     <row r="178">
@@ -3919,112 +3922,112 @@
       <c r="A319" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="2" t="s">
-        <v>1</v>
+      <c r="B319" s="3">
+        <v>21.7895009</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>1</v>
+      <c r="B320" s="3">
+        <v>31.14002958</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>1</v>
+      <c r="B321" s="3">
+        <v>25.28387047</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="2" t="s">
-        <v>1</v>
+      <c r="B322" s="3">
+        <v>14.2210226</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>1</v>
+      <c r="B323" s="3">
+        <v>4.964569325</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>1</v>
+      <c r="B324" s="3">
+        <v>1.744825539</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="2" t="s">
-        <v>1</v>
+      <c r="B325" s="3">
+        <v>0.3245065495</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>1</v>
+      <c r="B326" s="3">
+        <v>0.1620220095</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="2" t="s">
-        <v>1</v>
+      <c r="B327" s="3">
+        <v>0.2786450994</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>1</v>
+      <c r="B328" s="3">
+        <v>0.04097673279</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="2" t="s">
-        <v>1</v>
+      <c r="B329" s="3">
+        <v>0.00955948941</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="2" t="s">
-        <v>1</v>
+      <c r="B330" s="3">
+        <v>0.02864060943</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="2" t="s">
-        <v>1</v>
+      <c r="B331" s="3">
+        <v>0.01163400072</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>1</v>
+      <c r="B332" s="3">
+        <v>0.01</v>
       </c>
     </row>
     <row r="333">

--- a/data/wwinchance.xlsx
+++ b/data/wwinchance.xlsx
@@ -11,110 +11,110 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="364">
+  <si>
+    <t>Richmond Spiders</t>
+  </si>
+  <si>
+    <t>Rhode Island Rams</t>
+  </si>
+  <si>
+    <t>George Mason Patriots</t>
+  </si>
   <si>
     <t>Davidson Wildcats</t>
   </si>
   <si>
+    <t>Saint Joseph's Hawks</t>
+  </si>
+  <si>
+    <t>La Salle Explorers</t>
+  </si>
+  <si>
+    <t>Dayton Flyers</t>
+  </si>
+  <si>
+    <t>George Washington Revolutionaries</t>
+  </si>
+  <si>
+    <t>Loyola Chicago Ramblers</t>
+  </si>
+  <si>
+    <t>St. Bonaventure Bonnies</t>
+  </si>
+  <si>
+    <t>Duquesne Dukes</t>
+  </si>
+  <si>
+    <t>Saint Louis Billikens</t>
+  </si>
+  <si>
+    <t>Fordham Rams</t>
+  </si>
+  <si>
+    <t>VCU Rams</t>
+  </si>
+  <si>
+    <t>Louisville Cardinals</t>
+  </si>
+  <si>
+    <t>North Carolina Tar Heels</t>
+  </si>
+  <si>
+    <t>Duke Blue Devils</t>
+  </si>
+  <si>
+    <t>NC State Wolfpack</t>
+  </si>
+  <si>
+    <t>Notre Dame Fighting Irish</t>
+  </si>
+  <si>
+    <t>Virginia Tech Hokies</t>
+  </si>
+  <si>
+    <t>Syracuse Orange</t>
+  </si>
+  <si>
+    <t>Virginia Cavaliers</t>
+  </si>
+  <si>
+    <t>Clemson Tigers</t>
+  </si>
+  <si>
+    <t>California Golden Bears</t>
+  </si>
+  <si>
+    <t>Stanford Cardinal</t>
+  </si>
+  <si>
+    <t>Georgia Tech Yellow Jackets</t>
+  </si>
+  <si>
+    <t>Miami Hurricanes</t>
+  </si>
+  <si>
+    <t>Florida State Seminoles</t>
+  </si>
+  <si>
+    <t>Wake Forest Demon Deacons</t>
+  </si>
+  <si>
+    <t>Boston College Eagles</t>
+  </si>
+  <si>
+    <t>Pittsburgh Panthers</t>
+  </si>
+  <si>
+    <t>SMU Mustangs</t>
+  </si>
+  <si>
+    <t>Binghamton Bearcats</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>Dayton Flyers</t>
-  </si>
-  <si>
-    <t>Duquesne Dukes</t>
-  </si>
-  <si>
-    <t>Fordham Rams</t>
-  </si>
-  <si>
-    <t>George Mason Patriots</t>
-  </si>
-  <si>
-    <t>George Washington Revolutionaries</t>
-  </si>
-  <si>
-    <t>La Salle Explorers</t>
-  </si>
-  <si>
-    <t>Loyola Chicago Ramblers</t>
-  </si>
-  <si>
-    <t>Rhode Island Rams</t>
-  </si>
-  <si>
-    <t>Richmond Spiders</t>
-  </si>
-  <si>
-    <t>Saint Louis Billikens</t>
-  </si>
-  <si>
-    <t>St. Bonaventure Bonnies</t>
-  </si>
-  <si>
-    <t>Saint Joseph's Hawks</t>
-  </si>
-  <si>
-    <t>VCU Rams</t>
-  </si>
-  <si>
-    <t>Boston College Eagles</t>
-  </si>
-  <si>
-    <t>California Golden Bears</t>
-  </si>
-  <si>
-    <t>Clemson Tigers</t>
-  </si>
-  <si>
-    <t>Duke Blue Devils</t>
-  </si>
-  <si>
-    <t>Florida State Seminoles</t>
-  </si>
-  <si>
-    <t>Georgia Tech Yellow Jackets</t>
-  </si>
-  <si>
-    <t>Louisville Cardinals</t>
-  </si>
-  <si>
-    <t>Miami Hurricanes</t>
-  </si>
-  <si>
-    <t>NC State Wolfpack</t>
-  </si>
-  <si>
-    <t>North Carolina Tar Heels</t>
-  </si>
-  <si>
-    <t>Notre Dame Fighting Irish</t>
-  </si>
-  <si>
-    <t>Pittsburgh Panthers</t>
-  </si>
-  <si>
-    <t>SMU Mustangs</t>
-  </si>
-  <si>
-    <t>Stanford Cardinal</t>
-  </si>
-  <si>
-    <t>Syracuse Orange</t>
-  </si>
-  <si>
-    <t>Virginia Cavaliers</t>
-  </si>
-  <si>
-    <t>Virginia Tech Hokies</t>
-  </si>
-  <si>
-    <t>Wake Forest Demon Deacons</t>
-  </si>
-  <si>
-    <t>Binghamton Bearcats</t>
-  </si>
-  <si>
     <t>Bryant Bulldogs</t>
   </si>
   <si>
@@ -214,108 +214,108 @@
     <t>Bellarmine Knights</t>
   </si>
   <si>
+    <t>UCLA Bruins</t>
+  </si>
+  <si>
+    <t>Michigan Wolverines</t>
+  </si>
+  <si>
+    <t>Iowa Hawkeyes</t>
+  </si>
+  <si>
+    <t>Ohio State Buckeyes</t>
+  </si>
+  <si>
+    <t>Minnesota Golden Gophers</t>
+  </si>
+  <si>
+    <t>Maryland Terrapins</t>
+  </si>
+  <si>
+    <t>Michigan State Spartans</t>
+  </si>
+  <si>
     <t>Illinois Fighting Illini</t>
   </si>
   <si>
+    <t>USC Trojans</t>
+  </si>
+  <si>
+    <t>Washington Huskies</t>
+  </si>
+  <si>
+    <t>Nebraska Cornhuskers</t>
+  </si>
+  <si>
+    <t>Oregon Ducks</t>
+  </si>
+  <si>
     <t>Indiana Hoosiers</t>
   </si>
   <si>
-    <t>Iowa Hawkeyes</t>
-  </si>
-  <si>
-    <t>Maryland Terrapins</t>
-  </si>
-  <si>
-    <t>Michigan Wolverines</t>
-  </si>
-  <si>
-    <t>Michigan State Spartans</t>
-  </si>
-  <si>
-    <t>Minnesota Golden Gophers</t>
-  </si>
-  <si>
-    <t>Nebraska Cornhuskers</t>
+    <t>Purdue Boilermakers</t>
+  </si>
+  <si>
+    <t>Wisconsin Badgers</t>
   </si>
   <si>
     <t>Northwestern Wildcats</t>
   </si>
   <si>
-    <t>Ohio State Buckeyes</t>
-  </si>
-  <si>
-    <t>Oregon Ducks</t>
-  </si>
-  <si>
     <t>Penn State Lady Lions</t>
   </si>
   <si>
-    <t>Purdue Boilermakers</t>
-  </si>
-  <si>
     <t>Rutgers Scarlet Knights</t>
   </si>
   <si>
-    <t>UCLA Bruins</t>
-  </si>
-  <si>
-    <t>USC Trojans</t>
-  </si>
-  <si>
-    <t>Washington Huskies</t>
-  </si>
-  <si>
-    <t>Wisconsin Badgers</t>
+    <t>TCU Horned Frogs</t>
+  </si>
+  <si>
+    <t>West Virginia Mountaineers</t>
+  </si>
+  <si>
+    <t>Oklahoma State Cowgirls</t>
+  </si>
+  <si>
+    <t>Baylor Bears</t>
+  </si>
+  <si>
+    <t>Texas Tech Lady Raiders</t>
+  </si>
+  <si>
+    <t>Iowa State Cyclones</t>
+  </si>
+  <si>
+    <t>Kansas Jayhawks</t>
+  </si>
+  <si>
+    <t>Colorado Buffaloes</t>
+  </si>
+  <si>
+    <t>BYU Cougars</t>
+  </si>
+  <si>
+    <t>Arizona State Sun Devils</t>
+  </si>
+  <si>
+    <t>Utah Utes</t>
+  </si>
+  <si>
+    <t>Kansas State Wildcats</t>
+  </si>
+  <si>
+    <t>Cincinnati Bearcats</t>
   </si>
   <si>
     <t>Arizona Wildcats</t>
   </si>
   <si>
-    <t>Arizona State Sun Devils</t>
-  </si>
-  <si>
-    <t>Baylor Bears</t>
-  </si>
-  <si>
-    <t>BYU Cougars</t>
-  </si>
-  <si>
-    <t>Cincinnati Bearcats</t>
-  </si>
-  <si>
-    <t>Colorado Buffaloes</t>
+    <t>UCF Knights</t>
   </si>
   <si>
     <t>Houston Cougars</t>
   </si>
   <si>
-    <t>Iowa State Cyclones</t>
-  </si>
-  <si>
-    <t>Kansas Jayhawks</t>
-  </si>
-  <si>
-    <t>Kansas State Wildcats</t>
-  </si>
-  <si>
-    <t>Oklahoma State Cowgirls</t>
-  </si>
-  <si>
-    <t>TCU Horned Frogs</t>
-  </si>
-  <si>
-    <t>Texas Tech Lady Raiders</t>
-  </si>
-  <si>
-    <t>UCF Knights</t>
-  </si>
-  <si>
-    <t>Utah Utes</t>
-  </si>
-  <si>
-    <t>West Virginia Mountaineers</t>
-  </si>
-  <si>
     <t>Butler Bulldogs</t>
   </si>
   <si>
@@ -379,33 +379,33 @@
     <t>Weber State Wildcats</t>
   </si>
   <si>
+    <t>High Point Panthers</t>
+  </si>
+  <si>
+    <t>Radford Highlanders</t>
+  </si>
+  <si>
+    <t>Longwood Lancers</t>
+  </si>
+  <si>
+    <t>Winthrop Eagles</t>
+  </si>
+  <si>
+    <t>Gardner-Webb Runnin' Bulldogs</t>
+  </si>
+  <si>
+    <t>South Carolina Upstate Spartans</t>
+  </si>
+  <si>
+    <t>UNC Asheville Bulldogs</t>
+  </si>
+  <si>
     <t>Charleston Southern Buccaneers</t>
   </si>
   <si>
-    <t>Gardner-Webb Runnin' Bulldogs</t>
-  </si>
-  <si>
-    <t>High Point Panthers</t>
-  </si>
-  <si>
-    <t>Longwood Lancers</t>
-  </si>
-  <si>
     <t>Presbyterian Blue Hose</t>
   </si>
   <si>
-    <t>Radford Highlanders</t>
-  </si>
-  <si>
-    <t>South Carolina Upstate Spartans</t>
-  </si>
-  <si>
-    <t>UNC Asheville Bulldogs</t>
-  </si>
-  <si>
-    <t>Winthrop Eagles</t>
-  </si>
-  <si>
     <t>Cal Poly Mustangs</t>
   </si>
   <si>
@@ -772,39 +772,39 @@
     <t>Wagner Seahawks</t>
   </si>
   <si>
+    <t>Lindenwood Lions</t>
+  </si>
+  <si>
+    <t>Western Illinois Leathernecks</t>
+  </si>
+  <si>
+    <t>Southern Indiana Screaming Eagles</t>
+  </si>
+  <si>
+    <t>Morehead State Eagles</t>
+  </si>
+  <si>
+    <t>SIU Edwardsville Cougars</t>
+  </si>
+  <si>
+    <t>Southeast Missouri State Redhawks</t>
+  </si>
+  <si>
+    <t>Little Rock Trojans</t>
+  </si>
+  <si>
+    <t>UT Martin Skyhawks</t>
+  </si>
+  <si>
+    <t>Tennessee Tech Golden Eagles</t>
+  </si>
+  <si>
+    <t>Tennessee State Lady Tigers</t>
+  </si>
+  <si>
     <t>Eastern Illinois Panthers</t>
   </si>
   <si>
-    <t>Lindenwood Lions</t>
-  </si>
-  <si>
-    <t>Little Rock Trojans</t>
-  </si>
-  <si>
-    <t>Morehead State Eagles</t>
-  </si>
-  <si>
-    <t>Southeast Missouri State Redhawks</t>
-  </si>
-  <si>
-    <t>SIU Edwardsville Cougars</t>
-  </si>
-  <si>
-    <t>Southern Indiana Screaming Eagles</t>
-  </si>
-  <si>
-    <t>Tennessee State Lady Tigers</t>
-  </si>
-  <si>
-    <t>Tennessee Tech Golden Eagles</t>
-  </si>
-  <si>
-    <t>UT Martin Skyhawks</t>
-  </si>
-  <si>
-    <t>Western Illinois Leathernecks</t>
-  </si>
-  <si>
     <t>American University Eagles</t>
   </si>
   <si>
@@ -835,54 +835,54 @@
     <t>Navy Midshipmen</t>
   </si>
   <si>
+    <t>South Carolina Gamecocks</t>
+  </si>
+  <si>
+    <t>Texas Longhorns</t>
+  </si>
+  <si>
+    <t>LSU Tigers</t>
+  </si>
+  <si>
+    <t>Vanderbilt Commodores</t>
+  </si>
+  <si>
+    <t>Oklahoma Sooners</t>
+  </si>
+  <si>
+    <t>Kentucky Wildcats</t>
+  </si>
+  <si>
+    <t>Georgia Lady Bulldogs</t>
+  </si>
+  <si>
+    <t>Ole Miss Rebels</t>
+  </si>
+  <si>
     <t>Alabama Crimson Tide</t>
   </si>
   <si>
+    <t>Tennessee Lady Volunteers</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M Aggies</t>
+  </si>
+  <si>
+    <t>Mississippi State Bulldogs</t>
+  </si>
+  <si>
+    <t>Florida Gators</t>
+  </si>
+  <si>
+    <t>Missouri Tigers</t>
+  </si>
+  <si>
+    <t>Auburn Tigers</t>
+  </si>
+  <si>
     <t>Arkansas Razorbacks</t>
   </si>
   <si>
-    <t>Auburn Tigers</t>
-  </si>
-  <si>
-    <t>Florida Gators</t>
-  </si>
-  <si>
-    <t>Georgia Lady Bulldogs</t>
-  </si>
-  <si>
-    <t>Kentucky Wildcats</t>
-  </si>
-  <si>
-    <t>LSU Tigers</t>
-  </si>
-  <si>
-    <t>Mississippi State Bulldogs</t>
-  </si>
-  <si>
-    <t>Missouri Tigers</t>
-  </si>
-  <si>
-    <t>Oklahoma Sooners</t>
-  </si>
-  <si>
-    <t>Ole Miss Rebels</t>
-  </si>
-  <si>
-    <t>South Carolina Gamecocks</t>
-  </si>
-  <si>
-    <t>Tennessee Lady Volunteers</t>
-  </si>
-  <si>
-    <t>Texas Longhorns</t>
-  </si>
-  <si>
-    <t>Texas A&amp;M Aggies</t>
-  </si>
-  <si>
-    <t>Vanderbilt Commodores</t>
-  </si>
-  <si>
     <t>Chattanooga Mocs</t>
   </si>
   <si>
@@ -943,6 +943,21 @@
     <t>UT Rio Grande Valley Vaqueros</t>
   </si>
   <si>
+    <t>North Dakota State Bison</t>
+  </si>
+  <si>
+    <t>South Dakota State Jackrabbits</t>
+  </si>
+  <si>
+    <t>South Dakota Coyotes</t>
+  </si>
+  <si>
+    <t>Oral Roberts Golden Eagles</t>
+  </si>
+  <si>
+    <t>St. Thomas-Minnesota Tommies</t>
+  </si>
+  <si>
     <t>Denver Pioneers</t>
   </si>
   <si>
@@ -952,22 +967,7 @@
     <t>North Dakota Fighting Hawks</t>
   </si>
   <si>
-    <t>North Dakota State Bison</t>
-  </si>
-  <si>
     <t>Omaha Mavericks</t>
-  </si>
-  <si>
-    <t>Oral Roberts Golden Eagles</t>
-  </si>
-  <si>
-    <t>South Dakota Coyotes</t>
-  </si>
-  <si>
-    <t>South Dakota State Jackrabbits</t>
-  </si>
-  <si>
-    <t>St. Thomas-Minnesota Tommies</t>
   </si>
   <si>
     <t>James Madison Dukes</t>
@@ -1109,8 +1109,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -1138,7 +1140,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1146,13 +1148,28 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1378,1335 +1395,1335 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="B1" s="2">
+        <v>30.96800296</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>31.53131288</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>20.77909579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>7.519119785</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3.82936398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2.103351684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.060327053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.6377355665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.6512458025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.6450243595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.1852502441</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.04130288715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.0260686074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.02279839898</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21.82766574</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>20.36993865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>24.87008066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10.98841513</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>6.386430835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4.37372281</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3.037368778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3.186954754</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2.472264741</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1.067725083</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.7180495447</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.4236029872</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.2392623993</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.02036638372</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.01815150531</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>1</v>
+      <c r="B34" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>1</v>
+      <c r="B35" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1</v>
+      <c r="B36" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1</v>
+      <c r="B37" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>1</v>
+      <c r="B38" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1</v>
+      <c r="B39" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>1</v>
+      <c r="B40" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>1</v>
+      <c r="B41" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1</v>
+      <c r="B42" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>1</v>
+      <c r="B43" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>1</v>
+      <c r="B44" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>1</v>
+      <c r="B45" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>1</v>
+      <c r="B46" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>1</v>
+      <c r="B47" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>1</v>
+      <c r="B48" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>1</v>
+      <c r="B49" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1</v>
+      <c r="B50" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>1</v>
+      <c r="B51" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>1</v>
+      <c r="B52" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>1</v>
+      <c r="B53" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>1</v>
+      <c r="B54" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="3">
-        <v>25.64638029</v>
+      <c r="B55" s="2">
+        <v>23.91258439</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="3">
-        <v>21.91696225</v>
+      <c r="B56" s="2">
+        <v>20.73753224</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="3">
-        <v>20.40964788</v>
+      <c r="B57" s="2">
+        <v>19.12520138</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="3">
-        <v>12.34721876</v>
+      <c r="B58" s="2">
+        <v>11.105138</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="3">
-        <v>8.286078591</v>
+      <c r="B59" s="2">
+        <v>10.08613164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="3">
-        <v>4.11929145</v>
+      <c r="B60" s="2">
+        <v>5.434605121</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="3">
-        <v>3.40906012</v>
+      <c r="B61" s="2">
+        <v>5.880356129</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="3">
-        <v>2.320461354</v>
+      <c r="B62" s="2">
+        <v>3.718451103</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="3">
-        <v>0.9693627795</v>
+      <c r="B63" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="3">
-        <v>0.3883976495</v>
+      <c r="B64" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="3">
-        <v>0.1865564575</v>
+      <c r="B65" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="3">
-        <v>5.82418543E-4</v>
+      <c r="B66" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>1</v>
+      <c r="B67" s="2">
+        <v>50.4096553</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>1</v>
+      <c r="B68" s="2">
+        <v>13.21989444</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>1</v>
+      <c r="B69" s="2">
+        <v>11.18193917</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>1</v>
+      <c r="B70" s="2">
+        <v>6.094925713</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>1</v>
+      <c r="B71" s="2">
+        <v>7.119614532</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>1</v>
+      <c r="B72" s="2">
+        <v>4.451942543</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>1</v>
+      <c r="B73" s="2">
+        <v>2.598527426</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>1</v>
+      <c r="B74" s="2">
+        <v>1.038684307</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>1</v>
+      <c r="B75" s="2">
+        <v>1.543299976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>1</v>
+      <c r="B76" s="2">
+        <v>1.344469229</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>1</v>
+      <c r="B77" s="2">
+        <v>0.4030407854</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>1</v>
+      <c r="B78" s="2">
+        <v>0.4238532956</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>1</v>
+      <c r="B79" s="2">
+        <v>0.1440590468</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>1</v>
+      <c r="B80" s="3">
+        <v>0.01862855512</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>1</v>
+      <c r="B81" s="3">
+        <v>0.007465681711</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>1</v>
+      <c r="B82" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>1</v>
+      <c r="B83" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>1</v>
+      <c r="B84" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>1</v>
+      <c r="B85" s="2">
+        <v>34.51595636</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>1</v>
+      <c r="B86" s="2">
+        <v>26.11847554</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>1</v>
+      <c r="B87" s="2">
+        <v>10.27082207</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>1</v>
+      <c r="B88" s="2">
+        <v>10.34954113</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>1</v>
+      <c r="B89" s="2">
+        <v>5.036519082</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>1</v>
+      <c r="B90" s="2">
+        <v>3.794619236</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>1</v>
+      <c r="B91" s="2">
+        <v>2.262744187</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>1</v>
+      <c r="B92" s="2">
+        <v>2.560490272</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>1</v>
+      <c r="B93" s="2">
+        <v>2.146267297</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>1</v>
+      <c r="B94" s="2">
+        <v>0.9818675113</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>1</v>
+      <c r="B95" s="2">
+        <v>1.449054868</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>1</v>
+      <c r="B96" s="2">
+        <v>0.3834660614</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>1</v>
+      <c r="B97" s="2">
+        <v>0.08776375078</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>1</v>
+      <c r="B98" s="7">
+        <v>0.0256707479</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>1</v>
+      <c r="B99" s="7">
+        <v>0.01545215828</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>1</v>
+      <c r="B100" s="7">
+        <v>0.001289729832</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>1</v>
+      <c r="B101" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>1</v>
+      <c r="B102" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>1</v>
+      <c r="B103" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>1</v>
+      <c r="B104" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>1</v>
+      <c r="B105" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>1</v>
+      <c r="B106" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>1</v>
+      <c r="B107" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>1</v>
+      <c r="B108" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>1</v>
+      <c r="B109" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>1</v>
+      <c r="B110" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>1</v>
+      <c r="B111" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>1</v>
+      <c r="B112" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>1</v>
+      <c r="B113" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>1</v>
+      <c r="B114" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>1</v>
+      <c r="B115" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>1</v>
+      <c r="B116" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>1</v>
+      <c r="B117" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>1</v>
+      <c r="B118" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>1</v>
+      <c r="B119" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>1</v>
+      <c r="B120" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>1</v>
+      <c r="B121" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>1</v>
+      <c r="B122" s="2">
+        <v>44.66233027</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>1</v>
+      <c r="B123" s="2">
+        <v>24.64864274</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>1</v>
+      <c r="B124" s="2">
+        <v>16.55151664</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>1</v>
+      <c r="B125" s="2">
+        <v>4.396651606</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>1</v>
+      <c r="B126" s="2">
+        <v>3.912728647</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>1</v>
+      <c r="B127" s="2">
+        <v>3.205035186</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1</v>
+      <c r="B128" s="2">
+        <v>1.974412679</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>1</v>
+      <c r="B129" s="2">
+        <v>0.6332538139</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>1</v>
+      <c r="B130" s="2">
+        <v>0.01542842184</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>1</v>
+      <c r="B131" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>1</v>
+      <c r="B132" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>1</v>
+      <c r="B133" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>1</v>
+      <c r="B134" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>1</v>
+      <c r="B135" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>1</v>
+      <c r="B136" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>1</v>
+      <c r="B137" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>1</v>
+      <c r="B138" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>1</v>
+      <c r="B139" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>1</v>
+      <c r="B140" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>1</v>
+      <c r="B141" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>1</v>
+      <c r="B142" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>1</v>
+      <c r="B143" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>1</v>
+      <c r="B144" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>1</v>
+      <c r="B145" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>1</v>
+      <c r="B146" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>1</v>
+      <c r="B147" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>1</v>
+      <c r="B148" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>1</v>
+      <c r="B149" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>1</v>
+      <c r="B150" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>1</v>
+      <c r="B151" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>1</v>
+      <c r="B152" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>1</v>
+      <c r="B153" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>1</v>
+      <c r="B154" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>1</v>
+      <c r="B155" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>1</v>
+      <c r="B156" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>1</v>
+      <c r="B157" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>1</v>
+      <c r="B158" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>1</v>
+      <c r="B159" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>1</v>
+      <c r="B160" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>1</v>
+      <c r="B161" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>1</v>
+      <c r="B162" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>1</v>
+      <c r="B163" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>1</v>
+      <c r="B164" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>1</v>
+      <c r="B165" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>1</v>
+      <c r="B166" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="8">
         <v>33.30592402</v>
       </c>
     </row>
@@ -2714,7 +2731,7 @@
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="8">
         <v>25.44474679</v>
       </c>
     </row>
@@ -2722,7 +2739,7 @@
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="8">
         <v>22.98369929</v>
       </c>
     </row>
@@ -2730,7 +2747,7 @@
       <c r="A170" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="8">
         <v>6.651479315</v>
       </c>
     </row>
@@ -2738,7 +2755,7 @@
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="8">
         <v>5.578145222</v>
       </c>
     </row>
@@ -2746,7 +2763,7 @@
       <c r="A172" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="8">
         <v>3.38479434</v>
       </c>
     </row>
@@ -2754,7 +2771,7 @@
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="8">
         <v>1.581866191</v>
       </c>
     </row>
@@ -2762,7 +2779,7 @@
       <c r="A174" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="8">
         <v>0.5772634753</v>
       </c>
     </row>
@@ -2770,7 +2787,7 @@
       <c r="A175" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="8">
         <v>0.3930827373</v>
       </c>
     </row>
@@ -2778,7 +2795,7 @@
       <c r="A176" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="8">
         <v>0.0</v>
       </c>
     </row>
@@ -2786,7 +2803,7 @@
       <c r="A177" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="8">
         <v>0.09899861912</v>
       </c>
     </row>
@@ -2794,1504 +2811,1504 @@
       <c r="A178" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>1</v>
+      <c r="B178" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>1</v>
+      <c r="B179" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>1</v>
+      <c r="B180" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>1</v>
+      <c r="B181" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>1</v>
+      <c r="B182" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>1</v>
+      <c r="B183" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>1</v>
+      <c r="B184" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>1</v>
+      <c r="B185" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>1</v>
+      <c r="B186" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>1</v>
+      <c r="B187" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>1</v>
+      <c r="B188" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>1</v>
+      <c r="B189" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>1</v>
+      <c r="B190" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>1</v>
+      <c r="B191" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>1</v>
+      <c r="B192" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>1</v>
+      <c r="B193" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>1</v>
+      <c r="B194" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>1</v>
+      <c r="B195" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>1</v>
+      <c r="B196" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>1</v>
+      <c r="B197" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>1</v>
+      <c r="B198" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>1</v>
+      <c r="B199" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>1</v>
+      <c r="B200" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>1</v>
+      <c r="B201" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>1</v>
+      <c r="B202" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>1</v>
+      <c r="B203" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>1</v>
+      <c r="B204" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>1</v>
+      <c r="B205" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>1</v>
+      <c r="B206" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>1</v>
+      <c r="B207" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>1</v>
+      <c r="B208" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>1</v>
+      <c r="B209" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="2" t="s">
-        <v>1</v>
+      <c r="B210" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>1</v>
+      <c r="B211" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>1</v>
+      <c r="B212" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>1</v>
+      <c r="B213" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>1</v>
+      <c r="B214" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>1</v>
+      <c r="B215" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>1</v>
+      <c r="B216" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>1</v>
+      <c r="B217" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>1</v>
+      <c r="B218" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>1</v>
+      <c r="B219" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>1</v>
+      <c r="B220" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>1</v>
+      <c r="B221" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>1</v>
+      <c r="B222" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>1</v>
+      <c r="B223" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>1</v>
+      <c r="B224" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>1</v>
+      <c r="B225" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>1</v>
+      <c r="B226" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>1</v>
+      <c r="B227" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>1</v>
+      <c r="B228" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>1</v>
+      <c r="B229" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>1</v>
+      <c r="B230" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>1</v>
+      <c r="B231" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>1</v>
+      <c r="B232" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>1</v>
+      <c r="B233" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>1</v>
+      <c r="B234" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>1</v>
+      <c r="B235" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>1</v>
+      <c r="B236" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>1</v>
+      <c r="B237" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>1</v>
+      <c r="B238" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>1</v>
+      <c r="B239" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>1</v>
+      <c r="B240" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>1</v>
+      <c r="B241" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>1</v>
+      <c r="B242" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>1</v>
+      <c r="B243" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>1</v>
+      <c r="B244" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>1</v>
+      <c r="B245" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>1</v>
+      <c r="B246" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>1</v>
+      <c r="B247" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>1</v>
+      <c r="B248" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>1</v>
+      <c r="B249" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>1</v>
+      <c r="B250" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>1</v>
+      <c r="B251" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="2" t="s">
-        <v>1</v>
+      <c r="B252" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>1</v>
+      <c r="B253" s="2">
+        <v>40.29581428</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>1</v>
+      <c r="B254" s="2">
+        <v>37.60491681</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>1</v>
+      <c r="B255" s="2">
+        <v>9.269893612</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>1</v>
+      <c r="B256" s="2">
+        <v>6.955870489</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>1</v>
+      <c r="B257" s="2">
+        <v>2.114589089</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>1</v>
+      <c r="B258" s="2">
+        <v>1.736851857</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>1</v>
+      <c r="B259" s="2">
+        <v>1.599426003</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>1</v>
+      <c r="B260" s="2">
+        <v>0.422637859</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>1</v>
+      <c r="B261" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="s">
+      <c r="A262" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>1</v>
+      <c r="B262" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="s">
+      <c r="A263" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>1</v>
+      <c r="B263" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>1</v>
+      <c r="B264" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>1</v>
+      <c r="B265" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>1</v>
+      <c r="B266" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>1</v>
+      <c r="B267" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>1</v>
+      <c r="B268" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>1</v>
+      <c r="B269" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>1</v>
+      <c r="B270" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>1</v>
+      <c r="B271" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>1</v>
+      <c r="B272" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="2" t="s">
-        <v>1</v>
+      <c r="B273" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="s">
+      <c r="A274" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B274" s="2" t="s">
-        <v>1</v>
+      <c r="B274" s="2">
+        <v>33.00270085</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="s">
+      <c r="A275" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>1</v>
+      <c r="B275" s="2">
+        <v>25.97928064</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="s">
+      <c r="A276" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>1</v>
+      <c r="B276" s="2">
+        <v>18.12989367</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="s">
+      <c r="A277" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>1</v>
+      <c r="B277" s="2">
+        <v>13.81298147</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="s">
+      <c r="A278" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B278" s="2" t="s">
-        <v>1</v>
+      <c r="B278" s="2">
+        <v>3.952059448</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="s">
+      <c r="A279" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>1</v>
+      <c r="B279" s="2">
+        <v>1.617692593</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="s">
+      <c r="A280" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>1</v>
+      <c r="B280" s="2">
+        <v>0.7939844274</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="s">
+      <c r="A281" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>1</v>
+      <c r="B281" s="2">
+        <v>1.026636192</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="s">
+      <c r="A282" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>1</v>
+      <c r="B282" s="2">
+        <v>0.6472293169</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="s">
+      <c r="A283" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>1</v>
+      <c r="B283" s="2">
+        <v>0.5438292497</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="s">
+      <c r="A284" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="2" t="s">
-        <v>1</v>
+      <c r="B284" s="2">
+        <v>0.3100007254</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="s">
+      <c r="A285" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>1</v>
+      <c r="B285" s="2">
+        <v>0.08259525542</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="s">
+      <c r="A286" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>1</v>
+      <c r="B286" s="2">
+        <v>0.08031367477</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="s">
+      <c r="A287" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>1</v>
+      <c r="B287" s="2">
+        <v>0.01262525934</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="s">
+      <c r="A288" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="2" t="s">
-        <v>1</v>
+      <c r="B288" s="2">
+        <v>0.006786776053</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="s">
+      <c r="A289" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>1</v>
+      <c r="B289" s="2">
+        <v>0.001390447826</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>1</v>
+      <c r="B290" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>1</v>
+      <c r="B291" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>1</v>
+      <c r="B292" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>1</v>
+      <c r="B293" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>1</v>
+      <c r="B294" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>1</v>
+      <c r="B295" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>1</v>
+      <c r="B296" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="2" t="s">
-        <v>1</v>
+      <c r="B297" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>1</v>
+      <c r="B298" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>1</v>
+      <c r="B299" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>1</v>
+      <c r="B300" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>1</v>
+      <c r="B301" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>1</v>
+      <c r="B302" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>1</v>
+      <c r="B303" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="2" t="s">
-        <v>1</v>
+      <c r="B304" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="2" t="s">
-        <v>1</v>
+      <c r="B305" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="2" t="s">
-        <v>1</v>
+      <c r="B306" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="2" t="s">
-        <v>1</v>
+      <c r="B307" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="2" t="s">
-        <v>1</v>
+      <c r="B308" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="2" t="s">
-        <v>1</v>
+      <c r="B309" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="s">
+      <c r="A310" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>1</v>
+      <c r="B310" s="2">
+        <v>51.06962059</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="s">
+      <c r="A311" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B311" s="2" t="s">
-        <v>1</v>
+      <c r="B311" s="2">
+        <v>35.80062081</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="s">
+      <c r="A312" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>1</v>
+      <c r="B312" s="2">
+        <v>9.08974295</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="s">
+      <c r="A313" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>1</v>
+      <c r="B313" s="2">
+        <v>2.082232546</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="s">
+      <c r="A314" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="B314" s="2" t="s">
-        <v>1</v>
+      <c r="B314" s="2">
+        <v>1.413972038</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="s">
+      <c r="A315" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B315" s="2" t="s">
-        <v>1</v>
+      <c r="B315" s="2">
+        <v>0.3627398658</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>1</v>
+      <c r="B316" s="2">
+        <v>0.1078046701</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="s">
+      <c r="A317" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>1</v>
+      <c r="B317" s="3">
+        <v>0.03984617678</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="s">
+      <c r="A318" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>1</v>
+      <c r="B318" s="3">
+        <v>0.03342035337</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="3">
-        <v>21.7895009</v>
+      <c r="B319" s="7">
+        <v>21.77046092</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="3">
-        <v>31.14002958</v>
+      <c r="B320" s="7">
+        <v>31.11281897</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="3">
-        <v>25.28387047</v>
+      <c r="B321" s="7">
+        <v>25.26177706</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="3">
-        <v>14.2210226</v>
+      <c r="B322" s="7">
+        <v>14.20859607</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="3">
-        <v>4.964569325</v>
+      <c r="B323" s="7">
+        <v>4.960231213</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="3">
-        <v>1.744825539</v>
+      <c r="B324" s="7">
+        <v>1.743300885</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="3">
-        <v>0.3245065495</v>
+      <c r="B325" s="7">
+        <v>0.3807938667</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="3">
-        <v>0.1620220095</v>
+      <c r="B326" s="7">
+        <v>0.1562836309</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="3">
-        <v>0.2786450994</v>
+      <c r="B327" s="7">
+        <v>0.2784016153</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="3">
-        <v>0.04097673279</v>
+      <c r="B328" s="7">
+        <v>0.09754500992</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B329" s="3">
-        <v>0.00955948941</v>
+      <c r="B329" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="3">
-        <v>0.02864060943</v>
+      <c r="B330" s="7">
+        <v>0.02861558285</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B331" s="3">
-        <v>0.01163400072</v>
+      <c r="B331" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="3">
-        <v>0.01</v>
+      <c r="B332" s="9">
+        <v>0.001175177965</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>1</v>
+      <c r="B333" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="2" t="s">
-        <v>1</v>
+      <c r="B334" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="2" t="s">
-        <v>1</v>
+      <c r="B335" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="2" t="s">
-        <v>1</v>
+      <c r="B336" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="2" t="s">
-        <v>1</v>
+      <c r="B337" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="2" t="s">
-        <v>1</v>
+      <c r="B338" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="2" t="s">
-        <v>1</v>
+      <c r="B339" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="2" t="s">
-        <v>1</v>
+      <c r="B340" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="2" t="s">
-        <v>1</v>
+      <c r="B341" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="2" t="s">
-        <v>1</v>
+      <c r="B342" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="2" t="s">
-        <v>1</v>
+      <c r="B343" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="2" t="s">
-        <v>1</v>
+      <c r="B344" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>1</v>
+      <c r="B345" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="2" t="s">
-        <v>1</v>
+      <c r="B346" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>1</v>
+      <c r="B347" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="2" t="s">
-        <v>1</v>
+      <c r="B348" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="2" t="s">
-        <v>1</v>
+      <c r="B349" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="2" t="s">
-        <v>1</v>
+      <c r="B350" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="2" t="s">
-        <v>1</v>
+      <c r="B351" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="2" t="s">
-        <v>1</v>
+      <c r="B352" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="2" t="s">
-        <v>1</v>
+      <c r="B353" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="2" t="s">
-        <v>1</v>
+      <c r="B354" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>1</v>
+      <c r="B355" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="2" t="s">
-        <v>1</v>
+      <c r="B356" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="2" t="s">
-        <v>1</v>
+      <c r="B357" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="2" t="s">
-        <v>1</v>
+      <c r="B358" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="2" t="s">
-        <v>1</v>
+      <c r="B359" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="2" t="s">
-        <v>1</v>
+      <c r="B360" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="2" t="s">
-        <v>1</v>
+      <c r="B361" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>1</v>
+      <c r="B362" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>1</v>
+      <c r="B363" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B364" s="2" t="s">
-        <v>1</v>
+      <c r="B364" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B365" s="2" t="s">
-        <v>1</v>
+      <c r="B365" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/wwinchance.xlsx
+++ b/data/wwinchance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="364">
   <si>
     <t>Richmond Spiders</t>
   </si>
@@ -109,39 +109,39 @@
     <t>SMU Mustangs</t>
   </si>
   <si>
+    <t>Vermont Catamounts</t>
+  </si>
+  <si>
+    <t>Maine Black Bears</t>
+  </si>
+  <si>
+    <t>NJIT Highlanders</t>
+  </si>
+  <si>
+    <t>UMBC Retrievers</t>
+  </si>
+  <si>
+    <t>Bryant Bulldogs</t>
+  </si>
+  <si>
     <t>Binghamton Bearcats</t>
   </si>
   <si>
+    <t>UAlbany Great Danes</t>
+  </si>
+  <si>
+    <t>New Hampshire Wildcats</t>
+  </si>
+  <si>
+    <t>UMass Lowell River Hawks</t>
+  </si>
+  <si>
+    <t>Charlotte 49ers</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>Bryant Bulldogs</t>
-  </si>
-  <si>
-    <t>Maine Black Bears</t>
-  </si>
-  <si>
-    <t>New Hampshire Wildcats</t>
-  </si>
-  <si>
-    <t>NJIT Highlanders</t>
-  </si>
-  <si>
-    <t>UAlbany Great Danes</t>
-  </si>
-  <si>
-    <t>UMass Lowell River Hawks</t>
-  </si>
-  <si>
-    <t>UMBC Retrievers</t>
-  </si>
-  <si>
-    <t>Vermont Catamounts</t>
-  </si>
-  <si>
-    <t>Charlotte 49ers</t>
-  </si>
-  <si>
     <t>East Carolina Pirates</t>
   </si>
   <si>
@@ -571,45 +571,45 @@
     <t>Yale Bulldogs</t>
   </si>
   <si>
+    <t>Fairfield Stags</t>
+  </si>
+  <si>
+    <t>Quinnipiac Bobcats</t>
+  </si>
+  <si>
+    <t>Merrimack Warriors</t>
+  </si>
+  <si>
+    <t>Iona Gaels</t>
+  </si>
+  <si>
+    <t>Siena Saints</t>
+  </si>
+  <si>
+    <t>Manhattan Jaspers</t>
+  </si>
+  <si>
+    <t>Mount St. Mary's Mountaineers</t>
+  </si>
+  <si>
+    <t>Sacred Heart Pioneers</t>
+  </si>
+  <si>
+    <t>Marist Red Foxes</t>
+  </si>
+  <si>
+    <t>Saint Peter's Peacocks</t>
+  </si>
+  <si>
     <t>Canisius Golden Griffins</t>
   </si>
   <si>
-    <t>Fairfield Stags</t>
-  </si>
-  <si>
-    <t>Iona Gaels</t>
-  </si>
-  <si>
-    <t>Manhattan Jaspers</t>
-  </si>
-  <si>
-    <t>Marist Red Foxes</t>
-  </si>
-  <si>
-    <t>Merrimack Warriors</t>
-  </si>
-  <si>
-    <t>Mount St. Mary's Mountaineers</t>
-  </si>
-  <si>
     <t>Niagara Purple Eagles</t>
   </si>
   <si>
-    <t>Quinnipiac Bobcats</t>
-  </si>
-  <si>
     <t>Rider Broncs</t>
   </si>
   <si>
-    <t>Sacred Heart Pioneers</t>
-  </si>
-  <si>
-    <t>Siena Saints</t>
-  </si>
-  <si>
-    <t>Saint Peter's Peacocks</t>
-  </si>
-  <si>
     <t>Akron Zips</t>
   </si>
   <si>
@@ -883,18 +883,21 @@
     <t>Arkansas Razorbacks</t>
   </si>
   <si>
+    <t>East Tennessee State Bucs</t>
+  </si>
+  <si>
     <t>Chattanooga Mocs</t>
   </si>
   <si>
-    <t>East Tennessee State Bucs</t>
+    <t>Wofford Terriers</t>
+  </si>
+  <si>
+    <t>Mercer Bears</t>
   </si>
   <si>
     <t>Furman Paladins</t>
   </si>
   <si>
-    <t>Mercer Bears</t>
-  </si>
-  <si>
     <t>Samford Bulldogs</t>
   </si>
   <si>
@@ -904,9 +907,6 @@
     <t>Western Carolina Catamounts</t>
   </si>
   <si>
-    <t>Wofford Terriers</t>
-  </si>
-  <si>
     <t>East Texas A&amp;M Lions</t>
   </si>
   <si>
@@ -1078,41 +1078,40 @@
     <t>Oregon State Beavers</t>
   </si>
   <si>
+    <t>Santa Clara Broncos</t>
+  </si>
+  <si>
+    <t>Pepperdine Waves</t>
+  </si>
+  <si>
+    <t>Portland Pilots</t>
+  </si>
+  <si>
+    <t>San Francisco Dons</t>
+  </si>
+  <si>
+    <t>Saint Mary's Gaels</t>
+  </si>
+  <si>
     <t>Pacific Tigers</t>
   </si>
   <si>
-    <t>Pepperdine Waves</t>
-  </si>
-  <si>
-    <t>Portland Pilots</t>
-  </si>
-  <si>
     <t>San Diego Toreros</t>
   </si>
   <si>
-    <t>San Francisco Dons</t>
-  </si>
-  <si>
-    <t>Santa Clara Broncos</t>
+    <t>Washington State Cougars</t>
   </si>
   <si>
     <t>Seattle U Redhawks</t>
-  </si>
-  <si>
-    <t>Saint Mary's Gaels</t>
-  </si>
-  <si>
-    <t>Washington State Cougars</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -1156,19 +1155,19 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>30.96800296</v>
+        <v>30.9471111</v>
       </c>
     </row>
     <row r="2">
@@ -1404,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>31.53131288</v>
+        <v>31.510041</v>
       </c>
     </row>
     <row r="3">
@@ -1412,7 +1411,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>20.77909579</v>
+        <v>20.76507764</v>
       </c>
     </row>
     <row r="4">
@@ -1420,7 +1419,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>7.519119785</v>
+        <v>7.514047182</v>
       </c>
     </row>
     <row r="5">
@@ -1428,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>3.82936398</v>
+        <v>3.759910714</v>
       </c>
     </row>
     <row r="6">
@@ -1436,7 +1435,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>2.103351684</v>
+        <v>2.056304597</v>
       </c>
     </row>
     <row r="7">
@@ -1444,7 +1443,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>1.060327053</v>
+        <v>1.059611728</v>
       </c>
     </row>
     <row r="8">
@@ -1452,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0.6377355665</v>
+        <v>0.6373053327</v>
       </c>
     </row>
     <row r="9">
@@ -1460,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>0.6512458025</v>
+        <v>0.6508064543</v>
       </c>
     </row>
     <row r="10">
@@ -1468,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>0.6450243595</v>
+        <v>0.6445892085</v>
       </c>
     </row>
     <row r="11">
@@ -1476,7 +1475,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1852502441</v>
+        <v>0.3538492492</v>
       </c>
     </row>
     <row r="12">
@@ -1484,23 +1483,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>0.04130288715</v>
+        <v>0.1013457937</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.0260686074</v>
+      <c r="B13" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
-        <v>0.02279839898</v>
+      <c r="B14" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -1508,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>21.82766574</v>
+        <v>21.46203756</v>
       </c>
     </row>
     <row r="16">
@@ -1516,7 +1515,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>20.36993865</v>
+        <v>20.02872839</v>
       </c>
     </row>
     <row r="17">
@@ -1524,7 +1523,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>24.87008066</v>
+        <v>24.45348997</v>
       </c>
     </row>
     <row r="18">
@@ -1532,7 +1531,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>10.98841513</v>
+        <v>10.80435174</v>
       </c>
     </row>
     <row r="19">
@@ -1540,7 +1539,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>6.386430835</v>
+        <v>7.378199358</v>
       </c>
     </row>
     <row r="20">
@@ -1548,7 +1547,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>4.37372281</v>
+        <v>4.214640481</v>
       </c>
     </row>
     <row r="21">
@@ -1556,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>3.037368778</v>
+        <v>2.892696472</v>
       </c>
     </row>
     <row r="22">
@@ -1564,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>3.186954754</v>
+        <v>3.133571104</v>
       </c>
     </row>
     <row r="23">
@@ -1572,7 +1571,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>2.472264741</v>
+        <v>2.430852633</v>
       </c>
     </row>
     <row r="24">
@@ -1580,15 +1579,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>1.067725083</v>
+        <v>1.731424234</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
-        <v>0.7180495447</v>
+      <c r="B25" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1596,7 +1595,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4236029872</v>
+        <v>0.7291897562</v>
       </c>
     </row>
     <row r="27">
@@ -1604,23 +1603,23 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2392623993</v>
+        <v>0.7408183056</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
-        <v>0.02036638372</v>
+      <c r="B28" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
-        <v>0.01815150531</v>
+      <c r="B29" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -1648,179 +1647,179 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="2">
+        <v>42.57775534</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="2">
+        <v>17.27942523</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="B35" s="2">
+        <v>10.36598199</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="2">
+        <v>9.680763</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="2">
+        <v>6.887409583</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="2">
+        <v>6.553576317</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="2">
+        <v>4.714884246</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>33</v>
+      <c r="B40" s="2">
+        <v>1.940204298</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>33</v>
+      <c r="B43" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>33</v>
+      <c r="B44" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>33</v>
+      <c r="B45" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>33</v>
+      <c r="B46" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>33</v>
+      <c r="B47" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>33</v>
+      <c r="B48" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>33</v>
+      <c r="B49" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>33</v>
+      <c r="B50" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>33</v>
+      <c r="B51" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>33</v>
+      <c r="B52" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>33</v>
+      <c r="B53" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>33</v>
+      <c r="B54" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="55">
@@ -1924,7 +1923,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>50.4096553</v>
+        <v>49.99054255</v>
       </c>
     </row>
     <row r="68">
@@ -1932,7 +1931,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>13.21989444</v>
+        <v>13.10998244</v>
       </c>
     </row>
     <row r="69">
@@ -1940,7 +1939,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>11.18193917</v>
+        <v>11.088971</v>
       </c>
     </row>
     <row r="70">
@@ -1948,7 +1947,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>6.094925713</v>
+        <v>6.347346852</v>
       </c>
     </row>
     <row r="71">
@@ -1956,7 +1955,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>7.119614532</v>
+        <v>7.060421085</v>
       </c>
     </row>
     <row r="72">
@@ -1964,7 +1963,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>4.451942543</v>
+        <v>4.308417246</v>
       </c>
     </row>
     <row r="73">
@@ -1972,7 +1971,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="2">
-        <v>2.598527426</v>
+        <v>2.527335796</v>
       </c>
     </row>
     <row r="74">
@@ -1980,7 +1979,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="2">
-        <v>1.038684307</v>
+        <v>1.501784999</v>
       </c>
     </row>
     <row r="75">
@@ -1988,7 +1987,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="2">
-        <v>1.543299976</v>
+        <v>1.530468769</v>
       </c>
     </row>
     <row r="76">
@@ -1996,15 +1995,15 @@
         <v>76</v>
       </c>
       <c r="B76" s="2">
-        <v>1.344469229</v>
+        <v>1.333291129</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="2">
-        <v>0.4030407854</v>
+      <c r="B77" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2012,7 +2011,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="2">
-        <v>0.4238532956</v>
+        <v>0.7555679215</v>
       </c>
     </row>
     <row r="79">
@@ -2020,23 +2019,23 @@
         <v>79</v>
       </c>
       <c r="B79" s="2">
-        <v>0.1440590468</v>
+        <v>0.4458702186</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="3">
-        <v>0.01862855512</v>
+      <c r="B80" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="3">
-        <v>0.007465681711</v>
+      <c r="B81" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2064,683 +2063,683 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B85" s="2">
-        <v>34.51595636</v>
+        <v>33.61904498</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B86" s="2">
-        <v>26.11847554</v>
+        <v>25.72295648</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B87" s="2">
-        <v>10.27082207</v>
+        <v>10.11528827</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B88" s="2">
-        <v>10.34954113</v>
+        <v>9.942403604</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B89" s="2">
-        <v>5.036519082</v>
+        <v>4.784179917</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B90" s="2">
-        <v>3.794619236</v>
+        <v>3.722856274</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B91" s="2">
-        <v>2.262744187</v>
+        <v>3.273002352</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B92" s="2">
-        <v>2.560490272</v>
+        <v>2.449470165</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B93" s="2">
-        <v>2.146267297</v>
+        <v>2.718729937</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B94" s="2">
-        <v>0.9818675113</v>
+        <v>1.393736916</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B95" s="2">
-        <v>1.449054868</v>
+        <v>1.396146007</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B96" s="2">
-        <v>0.3834660614</v>
+        <v>0.8621850956</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="2">
-        <v>0.08776375078</v>
+      <c r="B97" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="7">
-        <v>0.0256707479</v>
+      <c r="B98" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="7">
-        <v>0.01545215828</v>
+      <c r="B99" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="7">
-        <v>0.001289729832</v>
+      <c r="B100" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>33</v>
+      <c r="B101" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>33</v>
+      <c r="B102" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>33</v>
+      <c r="B103" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="5" t="s">
-        <v>33</v>
+      <c r="B104" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="5" t="s">
-        <v>33</v>
+      <c r="B105" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>33</v>
+      <c r="B106" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>33</v>
+      <c r="B107" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>33</v>
+      <c r="B108" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>33</v>
+      <c r="B109" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>33</v>
+      <c r="B110" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="5" t="s">
-        <v>33</v>
+      <c r="B111" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>33</v>
+      <c r="B112" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>33</v>
+      <c r="B113" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>33</v>
+      <c r="B114" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>33</v>
+      <c r="B115" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>33</v>
+      <c r="B116" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>33</v>
+      <c r="B117" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>33</v>
+      <c r="B118" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="5" t="s">
-        <v>33</v>
+      <c r="B119" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>33</v>
+      <c r="B120" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="5" t="s">
-        <v>33</v>
+      <c r="B121" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>122</v>
       </c>
       <c r="B122" s="2">
-        <v>44.66233027</v>
+        <v>43.97424915</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
       <c r="B123" s="2">
-        <v>24.64864274</v>
+        <v>24.50862959</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B124" s="2">
-        <v>16.55151664</v>
+        <v>16.45749808</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B125" s="2">
-        <v>4.396651606</v>
+        <v>4.371677046</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B126" s="2">
-        <v>3.912728647</v>
+        <v>3.890502943</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B127" s="2">
-        <v>3.205035186</v>
+        <v>4.204589184</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B128" s="2">
-        <v>1.974412679</v>
+        <v>1.963197306</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B129" s="2">
-        <v>0.6332538139</v>
+        <v>0.6296567047</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="2">
-        <v>0.01542842184</v>
+      <c r="B130" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="5" t="s">
-        <v>33</v>
+      <c r="B131" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="5" t="s">
-        <v>33</v>
+      <c r="B132" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>33</v>
+      <c r="B133" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>33</v>
+      <c r="B134" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>33</v>
+      <c r="B135" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="5" t="s">
-        <v>33</v>
+      <c r="B136" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="5" t="s">
-        <v>33</v>
+      <c r="B137" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="5" t="s">
-        <v>33</v>
+      <c r="B138" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="5" t="s">
-        <v>33</v>
+      <c r="B139" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>33</v>
+      <c r="B140" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="5" t="s">
-        <v>33</v>
+      <c r="B141" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="5" t="s">
-        <v>33</v>
+      <c r="B142" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="5" t="s">
-        <v>33</v>
+      <c r="B143" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="5" t="s">
-        <v>33</v>
+      <c r="B144" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="5" t="s">
-        <v>33</v>
+      <c r="B145" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="5" t="s">
-        <v>33</v>
+      <c r="B146" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="5" t="s">
-        <v>33</v>
+      <c r="B147" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="5" t="s">
-        <v>33</v>
+      <c r="B148" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="5" t="s">
-        <v>33</v>
+      <c r="B149" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="5" t="s">
-        <v>33</v>
+      <c r="B150" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="5" t="s">
-        <v>33</v>
+      <c r="B151" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="5" t="s">
-        <v>33</v>
+      <c r="B152" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="5" t="s">
-        <v>33</v>
+      <c r="B153" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B154" s="5" t="s">
-        <v>33</v>
+      <c r="B154" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B155" s="5" t="s">
-        <v>33</v>
+      <c r="B155" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B156" s="5" t="s">
-        <v>33</v>
+      <c r="B156" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>33</v>
+      <c r="B157" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B158" s="5" t="s">
-        <v>33</v>
+      <c r="B158" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="5" t="s">
-        <v>33</v>
+      <c r="B159" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B160" s="5" t="s">
-        <v>33</v>
+      <c r="B160" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B161" s="5" t="s">
-        <v>33</v>
+      <c r="B161" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>33</v>
+      <c r="B162" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>33</v>
+      <c r="B163" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>33</v>
+      <c r="B164" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="5" t="s">
-        <v>33</v>
+      <c r="B165" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>33</v>
+      <c r="B166" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B167" s="8">
-        <v>33.30592402</v>
+      <c r="B167" s="7">
+        <v>33.02227593</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B168" s="8">
-        <v>25.44474679</v>
+      <c r="B168" s="7">
+        <v>27.47372588</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169" s="8">
-        <v>22.98369929</v>
+      <c r="B169" s="7">
+        <v>23.82239459</v>
       </c>
     </row>
     <row r="170">
@@ -2748,15 +2747,15 @@
         <v>170</v>
       </c>
       <c r="B170" s="8">
-        <v>6.651479315</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="8">
-        <v>5.578145222</v>
+      <c r="B171" s="7">
+        <v>11.94615032</v>
       </c>
     </row>
     <row r="172">
@@ -2764,15 +2763,15 @@
         <v>172</v>
       </c>
       <c r="B172" s="8">
-        <v>3.38479434</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B173" s="8">
-        <v>1.581866191</v>
+      <c r="B173" s="7">
+        <v>3.735453278</v>
       </c>
     </row>
     <row r="174">
@@ -2780,7 +2779,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="8">
-        <v>0.5772634753</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="175">
@@ -2788,7 +2787,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="8">
-        <v>0.3930827373</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -2804,607 +2803,607 @@
         <v>177</v>
       </c>
       <c r="B177" s="8">
-        <v>0.09899861912</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B178" s="5" t="s">
-        <v>33</v>
+      <c r="B178" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B179" s="5" t="s">
-        <v>33</v>
+      <c r="B179" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="5" t="s">
-        <v>33</v>
+      <c r="B180" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B181" s="5" t="s">
-        <v>33</v>
+      <c r="B181" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B182" s="5" t="s">
-        <v>33</v>
+      <c r="B182" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B183" s="5" t="s">
-        <v>33</v>
+      <c r="B183" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B184" s="5" t="s">
-        <v>33</v>
+      <c r="B184" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B185" s="5" t="s">
-        <v>33</v>
+      <c r="B185" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B186" s="5" t="s">
-        <v>33</v>
+      <c r="B186" s="2">
+        <v>50.92139941</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B187" s="5" t="s">
-        <v>33</v>
+      <c r="B187" s="2">
+        <v>39.28104559</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B188" s="5" t="s">
-        <v>33</v>
+      <c r="B188" s="2">
+        <v>4.462875147</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B189" s="5" t="s">
-        <v>33</v>
+      <c r="B189" s="2">
+        <v>2.160465716</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B190" s="5" t="s">
-        <v>33</v>
+      <c r="B190" s="2">
+        <v>1.203788862</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B191" s="5" t="s">
-        <v>33</v>
+      <c r="B191" s="2">
+        <v>0.645690981</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B192" s="5" t="s">
-        <v>33</v>
+      <c r="B192" s="2">
+        <v>0.8256018588</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B193" s="5" t="s">
-        <v>33</v>
+      <c r="B193" s="2">
+        <v>0.2717534964</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="5" t="s">
-        <v>33</v>
+      <c r="B194" s="2">
+        <v>0.1715934204</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B195" s="5" t="s">
-        <v>33</v>
+      <c r="B195" s="2">
+        <v>0.0557855135</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B196" s="5" t="s">
-        <v>33</v>
+      <c r="B196" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B197" s="5" t="s">
-        <v>33</v>
+      <c r="B197" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>33</v>
+      <c r="B198" s="2">
+        <v>0.0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B199" s="5" t="s">
-        <v>33</v>
+      <c r="B199" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B200" s="5" t="s">
-        <v>33</v>
+      <c r="B200" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B201" s="5" t="s">
-        <v>33</v>
+      <c r="B201" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B202" s="5" t="s">
-        <v>33</v>
+      <c r="B202" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="5" t="s">
-        <v>33</v>
+      <c r="B203" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B204" s="5" t="s">
-        <v>33</v>
+      <c r="B204" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B205" s="5" t="s">
-        <v>33</v>
+      <c r="B205" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B206" s="5" t="s">
-        <v>33</v>
+      <c r="B206" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B207" s="5" t="s">
-        <v>33</v>
+      <c r="B207" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B208" s="5" t="s">
-        <v>33</v>
+      <c r="B208" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B209" s="5" t="s">
-        <v>33</v>
+      <c r="B209" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B210" s="5" t="s">
-        <v>33</v>
+      <c r="B210" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="5" t="s">
-        <v>33</v>
+      <c r="B211" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B212" s="5" t="s">
-        <v>33</v>
+      <c r="B212" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="5" t="s">
-        <v>33</v>
+      <c r="B213" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="5" t="s">
-        <v>33</v>
+      <c r="B214" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="5" t="s">
-        <v>33</v>
+      <c r="B215" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="5" t="s">
-        <v>33</v>
+      <c r="B216" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="5" t="s">
-        <v>33</v>
+      <c r="B217" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="5" t="s">
-        <v>33</v>
+      <c r="B218" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B219" s="5" t="s">
-        <v>33</v>
+      <c r="B219" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B220" s="5" t="s">
-        <v>33</v>
+      <c r="B220" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B221" s="5" t="s">
-        <v>33</v>
+      <c r="B221" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B222" s="5" t="s">
-        <v>33</v>
+      <c r="B222" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B223" s="5" t="s">
-        <v>33</v>
+      <c r="B223" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="5" t="s">
-        <v>33</v>
+      <c r="B224" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B225" s="5" t="s">
-        <v>33</v>
+      <c r="B225" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B226" s="5" t="s">
-        <v>33</v>
+      <c r="B226" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B227" s="5" t="s">
-        <v>33</v>
+      <c r="B227" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B228" s="5" t="s">
-        <v>33</v>
+      <c r="B228" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B229" s="5" t="s">
-        <v>33</v>
+      <c r="B229" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B230" s="5" t="s">
-        <v>33</v>
+      <c r="B230" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B231" s="5" t="s">
-        <v>33</v>
+      <c r="B231" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B232" s="5" t="s">
-        <v>33</v>
+      <c r="B232" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B233" s="5" t="s">
-        <v>33</v>
+      <c r="B233" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B234" s="5" t="s">
-        <v>33</v>
+      <c r="B234" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B235" s="5" t="s">
-        <v>33</v>
+      <c r="B235" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B236" s="5" t="s">
-        <v>33</v>
+      <c r="B236" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B237" s="5" t="s">
-        <v>33</v>
+      <c r="B237" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B238" s="5" t="s">
-        <v>33</v>
+      <c r="B238" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B239" s="5" t="s">
-        <v>33</v>
+      <c r="B239" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B240" s="5" t="s">
-        <v>33</v>
+      <c r="B240" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B241" s="5" t="s">
-        <v>33</v>
+      <c r="B241" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B242" s="5" t="s">
-        <v>33</v>
+      <c r="B242" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B243" s="5" t="s">
-        <v>33</v>
+      <c r="B243" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B244" s="5" t="s">
-        <v>33</v>
+      <c r="B244" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B245" s="5" t="s">
-        <v>33</v>
+      <c r="B245" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B246" s="5" t="s">
-        <v>33</v>
+      <c r="B246" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B247" s="5" t="s">
-        <v>33</v>
+      <c r="B247" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B248" s="5" t="s">
-        <v>33</v>
+      <c r="B248" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B249" s="5" t="s">
-        <v>33</v>
+      <c r="B249" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B250" s="5" t="s">
-        <v>33</v>
+      <c r="B250" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B251" s="5" t="s">
-        <v>33</v>
+      <c r="B251" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B252" s="5" t="s">
-        <v>33</v>
+      <c r="B252" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="253">
@@ -3412,7 +3411,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="2">
-        <v>40.29581428</v>
+        <v>39.70360469</v>
       </c>
     </row>
     <row r="254">
@@ -3420,7 +3419,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="2">
-        <v>37.60491681</v>
+        <v>37.05225415</v>
       </c>
     </row>
     <row r="255">
@@ -3428,7 +3427,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="2">
-        <v>9.269893612</v>
+        <v>8.864494224</v>
       </c>
     </row>
     <row r="256">
@@ -3436,7 +3435,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="2">
-        <v>6.955870489</v>
+        <v>6.679377824</v>
       </c>
     </row>
     <row r="257">
@@ -3444,7 +3443,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="2">
-        <v>2.114589089</v>
+        <v>3.890887124</v>
       </c>
     </row>
     <row r="258">
@@ -3452,23 +3451,23 @@
         <v>258</v>
       </c>
       <c r="B258" s="2">
-        <v>1.736851857</v>
+        <v>3.809381985</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B259" s="2">
-        <v>1.599426003</v>
+      <c r="B259" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B260" s="2">
-        <v>0.422637859</v>
+      <c r="B260" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="261">
@@ -3480,7 +3479,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="6" t="s">
+      <c r="A262" s="5" t="s">
         <v>262</v>
       </c>
       <c r="B262" s="4">
@@ -3488,7 +3487,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="5" t="s">
         <v>263</v>
       </c>
       <c r="B263" s="4">
@@ -3499,520 +3498,520 @@
       <c r="A264" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B264" s="5" t="s">
-        <v>33</v>
+      <c r="B264" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B265" s="5" t="s">
-        <v>33</v>
+      <c r="B265" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B266" s="5" t="s">
-        <v>33</v>
+      <c r="B266" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B267" s="5" t="s">
-        <v>33</v>
+      <c r="B267" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B268" s="5" t="s">
-        <v>33</v>
+      <c r="B268" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B269" s="5" t="s">
-        <v>33</v>
+      <c r="B269" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B270" s="5" t="s">
-        <v>33</v>
+      <c r="B270" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B271" s="5" t="s">
-        <v>33</v>
+      <c r="B271" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="5" t="s">
-        <v>33</v>
+      <c r="B272" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B273" s="5" t="s">
-        <v>33</v>
+      <c r="B273" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="6" t="s">
+      <c r="A274" s="5" t="s">
         <v>274</v>
       </c>
       <c r="B274" s="2">
-        <v>33.00270085</v>
+        <v>31.86380811</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="s">
+      <c r="A275" s="5" t="s">
         <v>275</v>
       </c>
       <c r="B275" s="2">
-        <v>25.97928064</v>
+        <v>25.65962433</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="s">
+      <c r="A276" s="5" t="s">
         <v>276</v>
       </c>
       <c r="B276" s="2">
-        <v>18.12989367</v>
+        <v>18.16353316</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="s">
+      <c r="A277" s="5" t="s">
         <v>277</v>
       </c>
       <c r="B277" s="2">
-        <v>13.81298147</v>
+        <v>13.83861105</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="s">
+      <c r="A278" s="5" t="s">
         <v>278</v>
       </c>
       <c r="B278" s="2">
-        <v>3.952059448</v>
+        <v>3.824733722</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="s">
+      <c r="A279" s="5" t="s">
         <v>279</v>
       </c>
       <c r="B279" s="2">
-        <v>1.617692593</v>
+        <v>2.703784652</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="5" t="s">
         <v>280</v>
       </c>
       <c r="B280" s="2">
-        <v>0.7939844274</v>
+        <v>0.7336659712</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="s">
+      <c r="A281" s="5" t="s">
         <v>281</v>
       </c>
       <c r="B281" s="2">
-        <v>1.026636192</v>
+        <v>1.35092547</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="6" t="s">
+      <c r="A282" s="5" t="s">
         <v>282</v>
       </c>
       <c r="B282" s="2">
-        <v>0.6472293169</v>
+        <v>1.057294378</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="s">
+      <c r="A283" s="5" t="s">
         <v>283</v>
       </c>
       <c r="B283" s="2">
-        <v>0.5438292497</v>
+        <v>0.5271574934</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="6" t="s">
+      <c r="A284" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B284" s="2">
-        <v>0.3100007254</v>
+      <c r="B284" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="6" t="s">
+      <c r="A285" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B285" s="2">
-        <v>0.08259525542</v>
+      <c r="B285" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="s">
+      <c r="A286" s="5" t="s">
         <v>286</v>
       </c>
       <c r="B286" s="2">
-        <v>0.08031367477</v>
+        <v>0.2427007426</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="6" t="s">
+      <c r="A287" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B287" s="2">
-        <v>0.01262525934</v>
+      <c r="B287" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B288" s="2">
-        <v>0.006786776053</v>
+      <c r="B288" s="3">
+        <v>0.03416092285</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="s">
+      <c r="A289" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B289" s="2">
-        <v>0.001390447826</v>
+      <c r="B289" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B290" s="5" t="s">
-        <v>33</v>
+      <c r="B290" s="2">
+        <v>23.45460535</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B291" s="5" t="s">
-        <v>33</v>
+      <c r="B291" s="2">
+        <v>24.35923055</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B292" s="5" t="s">
-        <v>33</v>
+      <c r="B292" s="2">
+        <v>14.47595702</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B293" s="5" t="s">
-        <v>33</v>
+      <c r="B293" s="2">
+        <v>12.74450842</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B294" s="5" t="s">
-        <v>33</v>
+      <c r="B294" s="2">
+        <v>11.25782207</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="5" t="s">
-        <v>33</v>
+      <c r="B295" s="2">
+        <v>8.271979215</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B296" s="5" t="s">
-        <v>33</v>
+      <c r="B296" s="2">
+        <v>5.103554589</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B297" s="5" t="s">
-        <v>33</v>
+      <c r="B297" s="2">
+        <v>0.3323427843</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B298" s="5" t="s">
-        <v>33</v>
+      <c r="B298" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B299" s="5" t="s">
-        <v>33</v>
+      <c r="B299" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B300" s="5" t="s">
-        <v>33</v>
+      <c r="B300" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B301" s="5" t="s">
-        <v>33</v>
+      <c r="B301" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B302" s="5" t="s">
-        <v>33</v>
+      <c r="B302" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B303" s="5" t="s">
-        <v>33</v>
+      <c r="B303" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B304" s="5" t="s">
-        <v>33</v>
+      <c r="B304" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B305" s="5" t="s">
-        <v>33</v>
+      <c r="B305" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B306" s="5" t="s">
-        <v>33</v>
+      <c r="B306" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B307" s="5" t="s">
-        <v>33</v>
+      <c r="B307" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B308" s="5" t="s">
-        <v>33</v>
+      <c r="B308" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B309" s="5" t="s">
-        <v>33</v>
+      <c r="B309" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="6" t="s">
+      <c r="A310" s="5" t="s">
         <v>310</v>
       </c>
       <c r="B310" s="2">
-        <v>51.06962059</v>
+        <v>50.98111438</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="6" t="s">
+      <c r="A311" s="5" t="s">
         <v>311</v>
       </c>
       <c r="B311" s="2">
-        <v>35.80062081</v>
+        <v>35.85220222</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="s">
+      <c r="A312" s="5" t="s">
         <v>312</v>
       </c>
       <c r="B312" s="2">
-        <v>9.08974295</v>
+        <v>9.102839421</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="6" t="s">
+      <c r="A313" s="5" t="s">
         <v>313</v>
       </c>
       <c r="B313" s="2">
-        <v>2.082232546</v>
+        <v>2.08523262</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="6" t="s">
+      <c r="A314" s="5" t="s">
         <v>314</v>
       </c>
       <c r="B314" s="2">
-        <v>1.413972038</v>
+        <v>1.416009284</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="6" t="s">
+      <c r="A315" s="5" t="s">
         <v>315</v>
       </c>
       <c r="B315" s="2">
-        <v>0.3627398658</v>
+        <v>0.3632625001</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="6" t="s">
+      <c r="A316" s="5" t="s">
         <v>316</v>
       </c>
       <c r="B316" s="2">
-        <v>0.1078046701</v>
+        <v>0.1079599947</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="6" t="s">
+      <c r="A317" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B317" s="3">
-        <v>0.03984617678</v>
+      <c r="B317" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="6" t="s">
+      <c r="A318" s="5" t="s">
         <v>318</v>
       </c>
       <c r="B318" s="3">
-        <v>0.03342035337</v>
+        <v>0.091379582</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B319" s="7">
-        <v>21.77046092</v>
+      <c r="B319" s="9">
+        <v>21.70650728</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B320" s="7">
-        <v>31.11281897</v>
+      <c r="B320" s="9">
+        <v>31.0214209</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B321" s="7">
-        <v>25.26177706</v>
+      <c r="B321" s="9">
+        <v>25.18756721</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B322" s="7">
-        <v>14.20859607</v>
+      <c r="B322" s="9">
+        <v>14.16685642</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B323" s="7">
-        <v>4.960231213</v>
+      <c r="B323" s="9">
+        <v>5.139018633</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B324" s="7">
-        <v>1.743300885</v>
+      <c r="B324" s="9">
+        <v>1.692278429</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B325" s="7">
-        <v>0.3807938667</v>
+      <c r="B325" s="9">
+        <v>0.594517417</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B326" s="7">
-        <v>0.1562836309</v>
+      <c r="B326" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B327" s="7">
-        <v>0.2784016153</v>
+      <c r="B327" s="9">
+        <v>0.2688615981</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B328" s="7">
-        <v>0.09754500992</v>
+      <c r="B328" s="9">
+        <v>0.1920984922</v>
       </c>
     </row>
     <row r="329">
@@ -4027,8 +4026,8 @@
       <c r="A330" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B330" s="7">
-        <v>0.02861558285</v>
+      <c r="B330" s="9">
+        <v>0.03087362235</v>
       </c>
     </row>
     <row r="331">
@@ -4043,273 +4042,261 @@
       <c r="A332" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B332" s="9">
-        <v>0.001175177965</v>
+      <c r="B332" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B333" s="5" t="s">
-        <v>33</v>
+      <c r="B333" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B334" s="5" t="s">
-        <v>33</v>
+      <c r="B334" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B335" s="5" t="s">
-        <v>33</v>
+      <c r="B335" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B336" s="5" t="s">
-        <v>33</v>
+      <c r="B336" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B337" s="5" t="s">
-        <v>33</v>
+      <c r="B337" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B338" s="5" t="s">
-        <v>33</v>
+      <c r="B338" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B339" s="5" t="s">
-        <v>33</v>
+      <c r="B339" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B340" s="5" t="s">
-        <v>33</v>
+      <c r="B340" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B341" s="5" t="s">
-        <v>33</v>
+      <c r="B341" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B342" s="5" t="s">
-        <v>33</v>
+      <c r="B342" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B343" s="5" t="s">
-        <v>33</v>
+      <c r="B343" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B344" s="5" t="s">
-        <v>33</v>
+      <c r="B344" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B345" s="5" t="s">
-        <v>33</v>
+      <c r="B345" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B346" s="5" t="s">
-        <v>33</v>
+      <c r="B346" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="5" t="s">
-        <v>33</v>
+      <c r="B347" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B348" s="5" t="s">
-        <v>33</v>
+      <c r="B348" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B349" s="5" t="s">
-        <v>33</v>
+      <c r="B349" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B350" s="5" t="s">
-        <v>33</v>
+      <c r="B350" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B351" s="5" t="s">
-        <v>33</v>
+      <c r="B351" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B352" s="5" t="s">
-        <v>33</v>
+      <c r="B352" s="2">
+        <v>36.48224078</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B353" s="5" t="s">
-        <v>33</v>
+      <c r="B353" s="2">
+        <v>30.66673452</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B354" s="5" t="s">
-        <v>33</v>
+      <c r="B354" s="2">
+        <v>12.2664746</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B355" s="5" t="s">
-        <v>33</v>
+      <c r="B355" s="2">
+        <v>10.45443081</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B356" s="5" t="s">
-        <v>33</v>
+      <c r="B356" s="2">
+        <v>5.990559496</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B357" s="5" t="s">
-        <v>33</v>
+      <c r="B357" s="2">
+        <v>3.178914415</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B358" s="5" t="s">
-        <v>33</v>
+      <c r="B358" s="2">
+        <v>0.4436457605</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B359" s="5" t="s">
-        <v>33</v>
+      <c r="B359" s="2">
+        <v>0.1311857872</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B360" s="5" t="s">
-        <v>33</v>
+      <c r="B360" s="2">
+        <v>0.3086177444</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B361" s="5" t="s">
-        <v>33</v>
+      <c r="B361" s="2">
+        <v>0.02359688356</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B362" s="5" t="s">
-        <v>33</v>
+      <c r="B362" s="2">
+        <v>0.05320221621</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B363" s="5" t="s">
-        <v>33</v>
+      <c r="B363" s="2">
+        <v>3.96987382E-4</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B364" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B365" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="A364" s="1"/>
+      <c r="B364" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
